--- a/Excel/Case Study 2(Pivot Table).xlsx
+++ b/Excel/Case Study 2(Pivot Table).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771C8FAB-3ED5-4D68-A4CA-49B5AB9BD78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068B62D8-CBAF-4FD6-9CE5-818E153B6F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3C2F27DB-59A7-4E77-BCCC-EA28361B83B3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C2F27DB-59A7-4E77-BCCC-EA28361B83B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="16" r:id="rId5"/>
+    <pivotCache cacheId="6" r:id="rId4"/>
+    <pivotCache cacheId="7" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="67">
   <si>
     <t>Company</t>
   </si>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Average of Sales USD</t>
+  </si>
+  <si>
+    <t>Count of Sales Document</t>
+  </si>
+  <si>
+    <t>Count of Quantity</t>
   </si>
 </sst>
 </file>
@@ -467,16 +473,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1 2" xfId="1" xr:uid="{B1476517-8384-4BE4-9D5E-6902BBA44473}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -868,7 +880,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Region" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="America"/>
+        <s v="Europe"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Sales Document" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="24030" maxValue="68116" count="38">
@@ -2431,7 +2446,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="8010"/>
@@ -2445,7 +2460,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="1"/>
     <n v="8010"/>
@@ -2459,7 +2474,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="0"/>
     <n v="8010"/>
@@ -2473,7 +2488,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <n v="8010"/>
@@ -2487,7 +2502,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="0"/>
     <n v="8020"/>
@@ -2501,7 +2516,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="1"/>
     <n v="8020"/>
@@ -2515,7 +2530,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="2"/>
     <n v="8020"/>
@@ -2529,7 +2544,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="3"/>
     <x v="3"/>
     <n v="8010"/>
@@ -2543,7 +2558,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="3"/>
     <x v="4"/>
     <n v="8010"/>
@@ -2557,7 +2572,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="4"/>
     <x v="5"/>
     <n v="8020"/>
@@ -2571,7 +2586,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="4"/>
     <x v="6"/>
     <n v="8020"/>
@@ -2585,7 +2600,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="4"/>
     <x v="7"/>
     <n v="8020"/>
@@ -2599,7 +2614,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="4"/>
     <x v="8"/>
     <n v="8010"/>
@@ -2613,7 +2628,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="4"/>
     <x v="9"/>
     <n v="8010"/>
@@ -2627,7 +2642,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="5"/>
     <x v="10"/>
     <n v="8020"/>
@@ -2641,7 +2656,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="5"/>
     <x v="11"/>
     <n v="8020"/>
@@ -2655,7 +2670,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="6"/>
     <x v="1"/>
     <n v="8010"/>
@@ -2669,7 +2684,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="6"/>
     <x v="12"/>
     <n v="8010"/>
@@ -2683,7 +2698,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="6"/>
     <x v="13"/>
     <n v="8010"/>
@@ -2697,7 +2712,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="6"/>
     <x v="14"/>
     <n v="8020"/>
@@ -2711,7 +2726,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="6"/>
     <x v="15"/>
     <n v="8020"/>
@@ -2725,7 +2740,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="7"/>
     <x v="5"/>
     <n v="8010"/>
@@ -2739,7 +2754,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="7"/>
     <x v="6"/>
     <n v="8010"/>
@@ -2753,7 +2768,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="8"/>
     <x v="7"/>
     <n v="8010"/>
@@ -2767,7 +2782,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="8"/>
     <x v="8"/>
     <n v="8010"/>
@@ -2781,7 +2796,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="9"/>
     <x v="9"/>
     <n v="8020"/>
@@ -2795,7 +2810,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="9"/>
     <x v="10"/>
     <n v="8020"/>
@@ -2809,7 +2824,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="9"/>
     <x v="11"/>
     <n v="8020"/>
@@ -2823,7 +2838,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="10"/>
     <x v="16"/>
     <n v="8010"/>
@@ -2837,7 +2852,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="10"/>
     <x v="17"/>
     <n v="8010"/>
@@ -2851,7 +2866,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="11"/>
     <x v="18"/>
     <n v="8020"/>
@@ -2865,7 +2880,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="11"/>
     <x v="19"/>
     <n v="8020"/>
@@ -2879,7 +2894,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="11"/>
     <x v="20"/>
     <n v="8020"/>
@@ -2893,7 +2908,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="12"/>
     <x v="10"/>
     <n v="8010"/>
@@ -2907,7 +2922,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="12"/>
     <x v="11"/>
     <n v="8010"/>
@@ -2921,7 +2936,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="13"/>
     <x v="16"/>
     <n v="8020"/>
@@ -2935,7 +2950,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="13"/>
     <x v="17"/>
     <n v="8020"/>
@@ -2949,7 +2964,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="14"/>
     <x v="18"/>
     <n v="8010"/>
@@ -2963,7 +2978,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="14"/>
     <x v="19"/>
     <n v="8010"/>
@@ -2977,7 +2992,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="14"/>
     <x v="20"/>
     <n v="8010"/>
@@ -2991,7 +3006,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="15"/>
     <x v="21"/>
     <n v="8020"/>
@@ -3005,7 +3020,7 @@
   <r>
     <s v="1010US"/>
     <x v="0"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="15"/>
     <x v="22"/>
     <n v="8020"/>
@@ -3019,7 +3034,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="16"/>
     <x v="0"/>
     <n v="8020"/>
@@ -3033,7 +3048,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="16"/>
     <x v="1"/>
     <n v="8020"/>
@@ -3047,7 +3062,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="16"/>
     <x v="12"/>
     <n v="8020"/>
@@ -3061,7 +3076,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="16"/>
     <x v="13"/>
     <n v="8020"/>
@@ -3075,7 +3090,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="17"/>
     <x v="14"/>
     <n v="8020"/>
@@ -3089,7 +3104,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="17"/>
     <x v="15"/>
     <n v="8020"/>
@@ -3103,7 +3118,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="17"/>
     <x v="2"/>
     <n v="8020"/>
@@ -3117,7 +3132,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="18"/>
     <x v="3"/>
     <n v="8020"/>
@@ -3131,7 +3146,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="18"/>
     <x v="4"/>
     <n v="8020"/>
@@ -3145,7 +3160,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="18"/>
     <x v="5"/>
     <n v="8020"/>
@@ -3159,7 +3174,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="18"/>
     <x v="6"/>
     <n v="8020"/>
@@ -3173,7 +3188,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="18"/>
     <x v="7"/>
     <n v="8020"/>
@@ -3187,7 +3202,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="18"/>
     <x v="8"/>
     <n v="8020"/>
@@ -3201,7 +3216,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="18"/>
     <x v="9"/>
     <n v="8020"/>
@@ -3215,7 +3230,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="19"/>
     <x v="10"/>
     <n v="8010"/>
@@ -3229,7 +3244,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="19"/>
     <x v="11"/>
     <n v="8010"/>
@@ -3243,7 +3258,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="19"/>
     <x v="16"/>
     <n v="8010"/>
@@ -3257,7 +3272,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="19"/>
     <x v="17"/>
     <n v="8010"/>
@@ -3271,7 +3286,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="19"/>
     <x v="18"/>
     <n v="8010"/>
@@ -3285,7 +3300,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="19"/>
     <x v="19"/>
     <n v="8010"/>
@@ -3299,7 +3314,7 @@
   <r>
     <s v="1020US"/>
     <x v="1"/>
-    <s v="America"/>
+    <x v="0"/>
     <x v="19"/>
     <x v="20"/>
     <n v="8010"/>
@@ -3313,7 +3328,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="20"/>
     <x v="0"/>
     <n v="8060"/>
@@ -3327,7 +3342,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="20"/>
     <x v="1"/>
     <n v="8060"/>
@@ -3341,7 +3356,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="21"/>
     <x v="0"/>
     <n v="8060"/>
@@ -3355,7 +3370,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="21"/>
     <x v="1"/>
     <n v="8060"/>
@@ -3369,7 +3384,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="22"/>
     <x v="0"/>
     <n v="8050"/>
@@ -3383,7 +3398,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="22"/>
     <x v="1"/>
     <n v="8050"/>
@@ -3397,7 +3412,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="22"/>
     <x v="2"/>
     <n v="8050"/>
@@ -3411,7 +3426,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="23"/>
     <x v="3"/>
     <n v="8060"/>
@@ -3425,7 +3440,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="23"/>
     <x v="4"/>
     <n v="8060"/>
@@ -3439,7 +3454,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="24"/>
     <x v="3"/>
     <n v="8050"/>
@@ -3453,7 +3468,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="24"/>
     <x v="4"/>
     <n v="8050"/>
@@ -3467,7 +3482,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="24"/>
     <x v="7"/>
     <n v="8050"/>
@@ -3481,7 +3496,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="25"/>
     <x v="3"/>
     <n v="8060"/>
@@ -3495,7 +3510,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="25"/>
     <x v="4"/>
     <n v="8060"/>
@@ -3509,7 +3524,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="26"/>
     <x v="10"/>
     <n v="8050"/>
@@ -3523,7 +3538,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="26"/>
     <x v="11"/>
     <n v="8050"/>
@@ -3537,7 +3552,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="27"/>
     <x v="10"/>
     <n v="8060"/>
@@ -3551,7 +3566,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="27"/>
     <x v="11"/>
     <n v="8060"/>
@@ -3565,7 +3580,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="27"/>
     <x v="18"/>
     <n v="8060"/>
@@ -3579,7 +3594,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="28"/>
     <x v="10"/>
     <n v="8050"/>
@@ -3593,7 +3608,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="28"/>
     <x v="11"/>
     <n v="8050"/>
@@ -3607,7 +3622,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="29"/>
     <x v="17"/>
     <n v="8060"/>
@@ -3621,7 +3636,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="29"/>
     <x v="22"/>
     <n v="8060"/>
@@ -3635,7 +3650,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="30"/>
     <x v="11"/>
     <n v="8060"/>
@@ -3649,7 +3664,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="30"/>
     <x v="23"/>
     <n v="8060"/>
@@ -3663,7 +3678,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="31"/>
     <x v="11"/>
     <n v="8050"/>
@@ -3677,7 +3692,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="31"/>
     <x v="17"/>
     <n v="8050"/>
@@ -3691,7 +3706,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="31"/>
     <x v="22"/>
     <n v="8050"/>
@@ -3705,7 +3720,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="32"/>
     <x v="24"/>
     <n v="8060"/>
@@ -3719,7 +3734,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="32"/>
     <x v="25"/>
     <n v="8060"/>
@@ -3733,7 +3748,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="33"/>
     <x v="10"/>
     <n v="8050"/>
@@ -3747,7 +3762,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="33"/>
     <x v="11"/>
     <n v="8050"/>
@@ -3761,7 +3776,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="33"/>
     <x v="16"/>
     <n v="8050"/>
@@ -3775,7 +3790,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="34"/>
     <x v="17"/>
     <n v="8060"/>
@@ -3789,7 +3804,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="34"/>
     <x v="18"/>
     <n v="8060"/>
@@ -3803,7 +3818,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="35"/>
     <x v="19"/>
     <n v="8050"/>
@@ -3817,7 +3832,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="35"/>
     <x v="20"/>
     <n v="8050"/>
@@ -3831,7 +3846,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="36"/>
     <x v="21"/>
     <n v="8060"/>
@@ -3845,7 +3860,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="36"/>
     <x v="22"/>
     <n v="8060"/>
@@ -3859,7 +3874,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="36"/>
     <x v="26"/>
     <n v="8060"/>
@@ -3873,7 +3888,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="37"/>
     <x v="23"/>
     <n v="8050"/>
@@ -3887,7 +3902,7 @@
   <r>
     <s v="1040DE"/>
     <x v="2"/>
-    <s v="Europe"/>
+    <x v="1"/>
     <x v="37"/>
     <x v="27"/>
     <n v="8050"/>
@@ -3902,7 +3917,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F023387C-ED91-47BD-8E11-5FA5245915F7}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F023387C-ED91-47BD-8E11-5FA5245915F7}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O20:P31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0">
@@ -4055,80 +4070,96 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B167C823-BA6C-4329-B695-C12A7D83A00F}" name="PivotTable8" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C115:AP133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45303852-EBFB-4EB6-9409-416325AD8690}" name="PivotTable10" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C147:D152" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="39">
-        <item x="16"/>
-        <item x="17"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="29"/>
-        <item x="31"/>
-        <item x="30"/>
-        <item x="20"/>
-        <item x="22"/>
-        <item x="21"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="8"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
         <item x="0"/>
+        <item x="1"/>
         <item x="2"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Quantity" fld="9" subtotal="average" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F54FF75E-A4DD-4624-94EA-C9805E6590BC}" name="PivotTable15" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C238:E253" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="17">
         <item x="7"/>
@@ -4150,21 +4181,18 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="8"/>
   </rowFields>
-  <rowItems count="17">
+  <rowItems count="14">
     <i>
       <x/>
     </i>
     <i>
-      <x v="1"/>
-    </i>
-    <i>
       <x v="2"/>
     </i>
     <i>
@@ -4184,12 +4212,6 @@
     </i>
     <i>
       <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
     </i>
     <i>
       <x v="11"/>
@@ -4211,129 +4233,18 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="3"/>
+    <field x="2"/>
   </colFields>
-  <colItems count="39">
+  <colItems count="2">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of Sales USD" fld="10" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Count of Quantity" fld="9" subtotal="count" baseField="8" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -4347,8 +4258,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C94:D111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4478,12 +4389,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{263FB98E-3725-4EBF-B621-D9B8A3323DDE}" name="PivotTable6" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C83:E90" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item h="1" x="2"/>
         <item h="1" x="1"/>
@@ -4492,91 +4403,8 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
-      <items count="39">
-        <item h="1" x="16"/>
-        <item h="1" x="17"/>
-        <item h="1" x="19"/>
-        <item h="1" x="18"/>
-        <item h="1" x="29"/>
-        <item h="1" x="31"/>
-        <item h="1" x="30"/>
-        <item h="1" x="20"/>
-        <item h="1" x="22"/>
-        <item h="1" x="21"/>
-        <item h="1" x="35"/>
-        <item h="1" x="36"/>
-        <item h="1" x="37"/>
-        <item h="1" x="26"/>
-        <item h="1" x="27"/>
-        <item h="1" x="28"/>
-        <item h="1" x="32"/>
-        <item h="1" x="33"/>
-        <item h="1" x="34"/>
-        <item h="1" x="23"/>
-        <item h="1" x="24"/>
-        <item h="1" x="25"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="5"/>
-        <item x="6"/>
-        <item h="1" x="7"/>
-        <item h="1" x="9"/>
-        <item h="1" x="8"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisRow" numFmtId="164" showAll="0">
-      <items count="29">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="26"/>
-        <item x="23"/>
-        <item x="27"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -4586,171 +4414,18 @@
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="4"/>
+    <field x="1"/>
   </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="4" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C68:E79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="164" showAll="0">
-      <items count="29">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="26"/>
-        <item x="23"/>
-        <item x="27"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="17">
-        <item h="1" x="7"/>
-        <item h="1" x="13"/>
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="9"/>
-        <item h="1" x="11"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
@@ -4767,8 +4442,188 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324FA0CB-F108-452F-956F-BD634FC0600F}" name="PivotTable4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F36A9B7-2CC2-4747-B295-29C11DFEDD87}" name="PivotTable14" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C215:E233" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="39">
+        <item x="16"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Sales USD" fld="10" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="16">
+            <x v="22"/>
+            <x v="23"/>
+            <x v="24"/>
+            <x v="25"/>
+            <x v="26"/>
+            <x v="27"/>
+            <x v="28"/>
+            <x v="29"/>
+            <x v="30"/>
+            <x v="31"/>
+            <x v="32"/>
+            <x v="33"/>
+            <x v="34"/>
+            <x v="35"/>
+            <x v="36"/>
+            <x v="37"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324FA0CB-F108-452F-956F-BD634FC0600F}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C24:H64" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5037,8 +4892,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C17:E20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5119,8 +4974,748 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{035FB879-E106-40E1-9A43-93D438B27AF4}" name="PivotTable11" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C156:D185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="29">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C68:E79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="17">
+        <item h="1" x="7"/>
+        <item h="1" x="13"/>
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="11"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{263FB98E-3725-4EBF-B621-D9B8A3323DDE}" name="PivotTable6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C83:E90" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
+      <items count="39">
+        <item h="1" x="16"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="29"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="20"/>
+        <item h="1" x="22"/>
+        <item h="1" x="21"/>
+        <item h="1" x="35"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="32"/>
+        <item h="1" x="33"/>
+        <item h="1" x="34"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item h="1" x="25"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="5"/>
+        <item x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="9"/>
+        <item h="1" x="8"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B167C823-BA6C-4329-B695-C12A7D83A00F}" name="PivotTable8" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C115:AP133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="39">
+        <item x="16"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="39">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Sales USD" fld="10" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C11:D13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5192,21 +5787,128 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C8279AA-1521-48A6-A062-1EF528D5F734}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C137:D142" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+      <items count="5">
+        <item x="3"/>
         <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Sales Document" fld="3" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA3A419-CC1C-4656-B774-136C84C8EDBC}" name="PivotTable12" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C189:D191" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="39">
+        <item h="1" x="16"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="29"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="20"/>
+        <item h="1" x="22"/>
+        <item h="1" x="21"/>
+        <item h="1" x="35"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="32"/>
+        <item h="1" x="33"/>
+        <item h="1" x="34"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item h="1" x="25"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="5"/>
+        <item x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="9"/>
+        <item h="1" x="8"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -5217,11 +5919,11 @@
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="3"/>
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="2"/>
+      <x v="26"/>
     </i>
     <i t="grand">
       <x/>
@@ -5231,7 +5933,164 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFB86B-ABCE-49FA-AA44-1C6F1E6F10DA}" name="PivotTable13" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C196:E210" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="39">
+        <item h="1" x="16"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="29"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="20"/>
+        <item h="1" x="22"/>
+        <item h="1" x="21"/>
+        <item h="1" x="35"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="32"/>
+        <item h="1" x="33"/>
+        <item h="1" x="34"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item h="1" x="25"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="5"/>
+        <item x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="9"/>
+        <item h="1" x="8"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Quantity" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -5246,21 +6105,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B3927C07-72AD-450D-9244-F11244B3FAA5}" name="Sales2" displayName="Sales2" ref="A2:L107" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B3927C07-72AD-450D-9244-F11244B3FAA5}" name="Sales2" displayName="Sales2" ref="A2:L107" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A2:L107" xr:uid="{B3927C07-72AD-450D-9244-F11244B3FAA5}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8FF508AF-A4B1-4303-A717-709D017570C4}" name="Company" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{CF301B5E-B633-4B57-B1D9-B68DD6B89DC4}" name="Company Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{8AE0B328-BF2A-4594-8295-3E28B8ADA716}" name="Region" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{CE92F8AE-EF89-4726-9FB6-D3B87DADFBDE}" name="Sales Document" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{8A148EE5-F1F7-49CF-9569-EDE7168AD36C}" name="Document Date" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F473585C-8AC1-4D9B-B5BD-5C8F949193D6}" name="Customer Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{C82EB0CF-E39F-47F7-ABA1-D7595ABD164A}" name="Customer Name" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{22EBF275-AD47-4F61-841A-E664EF46DAF7}" name="Product Code" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{588CEC0C-3CB4-48F9-A086-A9C32B067A15}" name="Product Description" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{5EC74E3E-E918-4E84-A2C5-47D2FC9B5F03}" name="Quantity" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{15BBA754-97E5-40E6-BC17-B9E9F5E92F78}" name="Sales USD" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{E7D305A7-ADD5-4F92-A0E8-2F7023AF5B4D}" name="Total Sales" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{8FF508AF-A4B1-4303-A717-709D017570C4}" name="Company" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{CF301B5E-B633-4B57-B1D9-B68DD6B89DC4}" name="Company Name" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{8AE0B328-BF2A-4594-8295-3E28B8ADA716}" name="Region" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{CE92F8AE-EF89-4726-9FB6-D3B87DADFBDE}" name="Sales Document" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{8A148EE5-F1F7-49CF-9569-EDE7168AD36C}" name="Document Date" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{F473585C-8AC1-4D9B-B5BD-5C8F949193D6}" name="Customer Code" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{C82EB0CF-E39F-47F7-ABA1-D7595ABD164A}" name="Customer Name" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{22EBF275-AD47-4F61-841A-E664EF46DAF7}" name="Product Code" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{588CEC0C-3CB4-48F9-A086-A9C32B067A15}" name="Product Description" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{5EC74E3E-E918-4E84-A2C5-47D2FC9B5F03}" name="Quantity" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{15BBA754-97E5-40E6-BC17-B9E9F5E92F78}" name="Sales USD" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{E7D305A7-ADD5-4F92-A0E8-2F7023AF5B4D}" name="Total Sales" dataDxfId="2">
       <calculatedColumnFormula>Sales2[[#This Row],[Quantity]]*Sales2[[#This Row],[Sales USD]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10128,22 +10987,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718EE2BE-56F0-4B43-92C4-9B5664853DE8}">
-  <dimension ref="B4:AP136"/>
+  <dimension ref="B4:AP253"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -10210,7 +11073,7 @@
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6">
         <v>9858800</v>
       </c>
     </row>
@@ -10218,7 +11081,7 @@
       <c r="C7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7">
         <v>9858800</v>
       </c>
     </row>
@@ -10242,7 +11105,7 @@
       <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12">
         <v>42</v>
       </c>
     </row>
@@ -10250,7 +11113,7 @@
       <c r="C13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13">
         <v>42</v>
       </c>
     </row>
@@ -10285,10 +11148,10 @@
       <c r="C19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19">
         <v>880</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19">
         <v>880</v>
       </c>
     </row>
@@ -10296,10 +11159,10 @@
       <c r="C20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20">
         <v>880</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20">
         <v>880</v>
       </c>
     </row>
@@ -10343,13 +11206,10 @@
       <c r="C26" s="9">
         <v>24030</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19">
+      <c r="F26">
         <v>75</v>
       </c>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19">
+      <c r="H26">
         <v>75</v>
       </c>
     </row>
@@ -10357,13 +11217,10 @@
       <c r="C27" s="9">
         <v>24031</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19">
+      <c r="F27">
         <v>73.333333333333329</v>
       </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19">
+      <c r="H27">
         <v>73.333333333333329</v>
       </c>
     </row>
@@ -10371,13 +11228,10 @@
       <c r="C28" s="9">
         <v>25442</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19">
+      <c r="E28">
         <v>50</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19">
+      <c r="H28">
         <v>50</v>
       </c>
     </row>
@@ -10385,13 +11239,10 @@
       <c r="C29" s="9">
         <v>28112</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19">
+      <c r="F29">
         <v>55.714285714285715</v>
       </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19">
+      <c r="H29">
         <v>55.714285714285715</v>
       </c>
     </row>
@@ -10399,13 +11250,10 @@
       <c r="C30" s="9">
         <v>44015</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19">
+      <c r="G30">
         <v>65</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30">
         <v>65</v>
       </c>
     </row>
@@ -10413,13 +11261,10 @@
       <c r="C31" s="9">
         <v>44016</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31">
         <v>60</v>
       </c>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19">
+      <c r="H31">
         <v>60</v>
       </c>
     </row>
@@ -10427,13 +11272,10 @@
       <c r="C32" s="9">
         <v>44017</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19">
+      <c r="G32">
         <v>70</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32">
         <v>70</v>
       </c>
     </row>
@@ -10441,13 +11283,10 @@
       <c r="C33" s="9">
         <v>44030</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19">
+      <c r="G33">
         <v>60</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33">
         <v>60</v>
       </c>
     </row>
@@ -10455,13 +11294,10 @@
       <c r="C34" s="9">
         <v>44031</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34">
         <v>56.666666666666664</v>
       </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19">
+      <c r="H34">
         <v>56.666666666666664</v>
       </c>
     </row>
@@ -10469,13 +11305,10 @@
       <c r="C35" s="9">
         <v>44032</v>
       </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19">
+      <c r="G35">
         <v>65</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35">
         <v>65</v>
       </c>
     </row>
@@ -10483,13 +11316,10 @@
       <c r="C36" s="9">
         <v>45427</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36">
         <v>65</v>
       </c>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19">
+      <c r="H36">
         <v>65</v>
       </c>
     </row>
@@ -10497,13 +11327,10 @@
       <c r="C37" s="9">
         <v>45429</v>
       </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19">
+      <c r="G37">
         <v>70</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37">
         <v>70</v>
       </c>
     </row>
@@ -10511,13 +11338,10 @@
       <c r="C38" s="9">
         <v>45431</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38">
         <v>60</v>
       </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19">
+      <c r="H38">
         <v>60</v>
       </c>
     </row>
@@ -10525,13 +11349,10 @@
       <c r="C39" s="9">
         <v>45442</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39">
         <v>55</v>
       </c>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19">
+      <c r="H39">
         <v>55</v>
       </c>
     </row>
@@ -10539,13 +11360,10 @@
       <c r="C40" s="9">
         <v>45444</v>
       </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19">
+      <c r="G40">
         <v>63.333333333333336</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40">
         <v>63.333333333333336</v>
       </c>
     </row>
@@ -10553,13 +11371,10 @@
       <c r="C41" s="9">
         <v>45446</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41">
         <v>65</v>
       </c>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19">
+      <c r="H41">
         <v>65</v>
       </c>
     </row>
@@ -10567,13 +11382,10 @@
       <c r="C42" s="9">
         <v>48097</v>
       </c>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19">
+      <c r="G42">
         <v>65</v>
       </c>
-      <c r="H42" s="19">
+      <c r="H42">
         <v>65</v>
       </c>
     </row>
@@ -10581,13 +11393,10 @@
       <c r="C43" s="9">
         <v>48099</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43">
         <v>60</v>
       </c>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19">
+      <c r="H43">
         <v>60</v>
       </c>
     </row>
@@ -10595,13 +11404,10 @@
       <c r="C44" s="9">
         <v>48101</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19">
+      <c r="G44">
         <v>55</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44">
         <v>55</v>
       </c>
     </row>
@@ -10609,13 +11415,10 @@
       <c r="C45" s="9">
         <v>48112</v>
       </c>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19">
+      <c r="G45">
         <v>55</v>
       </c>
-      <c r="H45" s="19">
+      <c r="H45">
         <v>55</v>
       </c>
     </row>
@@ -10623,13 +11426,10 @@
       <c r="C46" s="9">
         <v>48114</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46">
         <v>66.666666666666671</v>
       </c>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19">
+      <c r="H46">
         <v>66.666666666666671</v>
       </c>
     </row>
@@ -10637,13 +11437,10 @@
       <c r="C47" s="9">
         <v>48116</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19">
+      <c r="G47">
         <v>60</v>
       </c>
-      <c r="H47" s="19">
+      <c r="H47">
         <v>60</v>
       </c>
     </row>
@@ -10651,13 +11448,10 @@
       <c r="C48" s="9">
         <v>65627</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19">
+      <c r="F48">
         <v>150</v>
       </c>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19">
+      <c r="H48">
         <v>150</v>
       </c>
     </row>
@@ -10665,13 +11459,10 @@
       <c r="C49" s="9">
         <v>65629</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19">
+      <c r="E49">
         <v>153.33333333333334</v>
       </c>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19">
+      <c r="H49">
         <v>153.33333333333334</v>
       </c>
     </row>
@@ -10679,13 +11470,10 @@
       <c r="C50" s="9">
         <v>65631</v>
       </c>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19">
+      <c r="F50">
         <v>155</v>
       </c>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19">
+      <c r="H50">
         <v>155</v>
       </c>
     </row>
@@ -10693,13 +11481,10 @@
       <c r="C51" s="9">
         <v>65662</v>
       </c>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19">
+      <c r="F51">
         <v>115</v>
       </c>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19">
+      <c r="H51">
         <v>115</v>
       </c>
     </row>
@@ -10707,15 +11492,13 @@
       <c r="C52" s="9">
         <v>65666</v>
       </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19">
+      <c r="E52">
         <v>140</v>
       </c>
-      <c r="F52" s="19">
+      <c r="F52">
         <v>160</v>
       </c>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19">
+      <c r="H52">
         <v>148</v>
       </c>
     </row>
@@ -10723,13 +11506,10 @@
       <c r="C53" s="9">
         <v>66015</v>
       </c>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19">
+      <c r="E53">
         <v>140</v>
       </c>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19">
+      <c r="H53">
         <v>140</v>
       </c>
     </row>
@@ -10737,13 +11517,10 @@
       <c r="C54" s="9">
         <v>66016</v>
       </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19">
+      <c r="F54">
         <v>123.33333333333333</v>
       </c>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19">
+      <c r="H54">
         <v>123.33333333333333</v>
       </c>
     </row>
@@ -10751,13 +11528,10 @@
       <c r="C55" s="9">
         <v>66017</v>
       </c>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19">
+      <c r="E55">
         <v>140</v>
       </c>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19">
+      <c r="H55">
         <v>140</v>
       </c>
     </row>
@@ -10765,13 +11539,10 @@
       <c r="C56" s="9">
         <v>66030</v>
       </c>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19">
+      <c r="E56">
         <v>135</v>
       </c>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19">
+      <c r="H56">
         <v>135</v>
       </c>
     </row>
@@ -10779,13 +11550,10 @@
       <c r="C57" s="9">
         <v>66031</v>
       </c>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19">
+      <c r="F57">
         <v>130</v>
       </c>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19">
+      <c r="H57">
         <v>130</v>
       </c>
     </row>
@@ -10793,13 +11561,10 @@
       <c r="C58" s="9">
         <v>66032</v>
       </c>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19">
+      <c r="E58">
         <v>155</v>
       </c>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19">
+      <c r="H58">
         <v>155</v>
       </c>
     </row>
@@ -10807,13 +11572,10 @@
       <c r="C59" s="9">
         <v>68097</v>
       </c>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19">
+      <c r="E59">
         <v>135</v>
       </c>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19">
+      <c r="H59">
         <v>135</v>
       </c>
     </row>
@@ -10821,13 +11583,10 @@
       <c r="C60" s="9">
         <v>68099</v>
       </c>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19">
+      <c r="F60">
         <v>143.33333333333334</v>
       </c>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19">
+      <c r="H60">
         <v>143.33333333333334</v>
       </c>
     </row>
@@ -10835,13 +11594,10 @@
       <c r="C61" s="9">
         <v>68101</v>
       </c>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19">
+      <c r="E61">
         <v>165</v>
       </c>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19">
+      <c r="H61">
         <v>165</v>
       </c>
     </row>
@@ -10849,13 +11605,10 @@
       <c r="C62" s="9">
         <v>68112</v>
       </c>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19">
+      <c r="E62">
         <v>150</v>
       </c>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19">
+      <c r="H62">
         <v>150</v>
       </c>
     </row>
@@ -10863,15 +11616,13 @@
       <c r="C63" s="9">
         <v>68116</v>
       </c>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19">
+      <c r="E63">
         <v>175</v>
       </c>
-      <c r="F63" s="19">
+      <c r="F63">
         <v>166.66666666666666</v>
       </c>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19">
+      <c r="H63">
         <v>170</v>
       </c>
     </row>
@@ -10879,19 +11630,19 @@
       <c r="C64" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64">
         <v>61</v>
       </c>
-      <c r="E64" s="19">
+      <c r="E64">
         <v>124.82758620689656</v>
       </c>
-      <c r="F64" s="19">
+      <c r="F64">
         <v>110.58823529411765</v>
       </c>
-      <c r="G64" s="19">
+      <c r="G64">
         <v>63.18181818181818</v>
       </c>
-      <c r="H64" s="19">
+      <c r="H64">
         <v>95.142857142857139</v>
       </c>
     </row>
@@ -10923,112 +11674,112 @@
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C70" s="20">
+      <c r="C70" s="19">
         <v>43986</v>
       </c>
-      <c r="D70" s="19">
+      <c r="D70">
         <v>256000</v>
       </c>
-      <c r="E70" s="19">
+      <c r="E70">
         <v>256000</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C71" s="20">
+      <c r="C71" s="19">
         <v>43989</v>
       </c>
-      <c r="D71" s="19">
+      <c r="D71">
         <v>100000</v>
       </c>
-      <c r="E71" s="19">
+      <c r="E71">
         <v>100000</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C72" s="20">
+      <c r="C72" s="19">
         <v>43991</v>
       </c>
-      <c r="D72" s="19">
+      <c r="D72">
         <v>144000</v>
       </c>
-      <c r="E72" s="19">
+      <c r="E72">
         <v>144000</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C73" s="20">
+      <c r="C73" s="19">
         <v>43993</v>
       </c>
-      <c r="D73" s="19">
+      <c r="D73">
         <v>361000</v>
       </c>
-      <c r="E73" s="19">
+      <c r="E73">
         <v>361000</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C74" s="20">
+      <c r="C74" s="19">
         <v>43996</v>
       </c>
-      <c r="D74" s="19">
+      <c r="D74">
         <v>361000</v>
       </c>
-      <c r="E74" s="19">
+      <c r="E74">
         <v>361000</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C75" s="20">
+      <c r="C75" s="19">
         <v>43998</v>
       </c>
-      <c r="D75" s="19">
+      <c r="D75">
         <v>340000</v>
       </c>
-      <c r="E75" s="19">
+      <c r="E75">
         <v>340000</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C76" s="20">
+      <c r="C76" s="19">
         <v>44000</v>
       </c>
-      <c r="D76" s="19">
+      <c r="D76">
         <v>169000</v>
       </c>
-      <c r="E76" s="19">
+      <c r="E76">
         <v>169000</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C77" s="20">
+      <c r="C77" s="19">
         <v>44002</v>
       </c>
-      <c r="D77" s="19">
+      <c r="D77">
         <v>196000</v>
       </c>
-      <c r="E77" s="19">
+      <c r="E77">
         <v>196000</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C78" s="20">
+      <c r="C78" s="19">
         <v>44003</v>
       </c>
-      <c r="D78" s="19">
+      <c r="D78">
         <v>196000</v>
       </c>
-      <c r="E78" s="19">
+      <c r="E78">
         <v>196000</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C79" s="20" t="s">
+      <c r="C79" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D79" s="19">
+      <c r="D79">
         <v>2123000</v>
       </c>
-      <c r="E79" s="19">
+      <c r="E79">
         <v>2123000</v>
       </c>
     </row>
@@ -11068,68 +11819,68 @@
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C85" s="20">
+      <c r="C85" s="19">
         <v>43984</v>
       </c>
-      <c r="D85" s="19">
+      <c r="D85">
         <v>172800</v>
       </c>
-      <c r="E85" s="19">
+      <c r="E85">
         <v>172800</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C86" s="20">
+      <c r="C86" s="19">
         <v>43985</v>
       </c>
-      <c r="D86" s="19">
+      <c r="D86">
         <v>235200</v>
       </c>
-      <c r="E86" s="19">
+      <c r="E86">
         <v>235200</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C87" s="20">
+      <c r="C87" s="19">
         <v>43986</v>
       </c>
-      <c r="D87" s="19">
+      <c r="D87">
         <v>256000</v>
       </c>
-      <c r="E87" s="19">
+      <c r="E87">
         <v>256000</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C88" s="20">
+      <c r="C88" s="19">
         <v>43987</v>
       </c>
-      <c r="D88" s="19">
+      <c r="D88">
         <v>72000</v>
       </c>
-      <c r="E88" s="19">
+      <c r="E88">
         <v>72000</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C89" s="20">
+      <c r="C89" s="19">
         <v>43988</v>
       </c>
-      <c r="D89" s="19">
+      <c r="D89">
         <v>480000</v>
       </c>
-      <c r="E89" s="19">
+      <c r="E89">
         <v>480000</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C90" s="20" t="s">
+      <c r="C90" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D90" s="19">
+      <c r="D90">
         <v>480000</v>
       </c>
-      <c r="E90" s="19">
+      <c r="E90">
         <v>480000</v>
       </c>
     </row>
@@ -11153,7 +11904,7 @@
       <c r="C95" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D95" s="19">
+      <c r="D95">
         <v>1759800</v>
       </c>
     </row>
@@ -11161,7 +11912,7 @@
       <c r="C96" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D96" s="19">
+      <c r="D96">
         <v>2118400</v>
       </c>
     </row>
@@ -11169,7 +11920,7 @@
       <c r="C97" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D97" s="19">
+      <c r="D97">
         <v>44500</v>
       </c>
     </row>
@@ -11177,7 +11928,7 @@
       <c r="C98" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D98" s="19">
+      <c r="D98">
         <v>250000</v>
       </c>
     </row>
@@ -11185,7 +11936,7 @@
       <c r="C99" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D99" s="19">
+      <c r="D99">
         <v>62500</v>
       </c>
     </row>
@@ -11193,7 +11944,7 @@
       <c r="C100" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D100" s="19">
+      <c r="D100">
         <v>264600</v>
       </c>
     </row>
@@ -11201,7 +11952,7 @@
       <c r="C101" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D101" s="19">
+      <c r="D101">
         <v>230400</v>
       </c>
     </row>
@@ -11209,7 +11960,7 @@
       <c r="C102" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D102" s="19">
+      <c r="D102">
         <v>70800</v>
       </c>
     </row>
@@ -11217,7 +11968,7 @@
       <c r="C103" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D103" s="19">
+      <c r="D103">
         <v>361200</v>
       </c>
     </row>
@@ -11225,7 +11976,7 @@
       <c r="C104" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D104" s="19">
+      <c r="D104">
         <v>2318100</v>
       </c>
     </row>
@@ -11233,7 +11984,7 @@
       <c r="C105" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D105" s="19">
+      <c r="D105">
         <v>470000</v>
       </c>
     </row>
@@ -11241,7 +11992,7 @@
       <c r="C106" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D106" s="19">
+      <c r="D106">
         <v>21600</v>
       </c>
     </row>
@@ -11249,7 +12000,7 @@
       <c r="C107" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D107" s="19">
+      <c r="D107">
         <v>525000</v>
       </c>
     </row>
@@ -11257,7 +12008,7 @@
       <c r="C108" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D108" s="19">
+      <c r="D108">
         <v>2123000</v>
       </c>
     </row>
@@ -11265,7 +12016,7 @@
       <c r="C109" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D109" s="19">
+      <c r="D109">
         <v>4146000</v>
       </c>
     </row>
@@ -11273,7 +12024,7 @@
       <c r="C110" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D110" s="19">
+      <c r="D110">
         <v>3064800</v>
       </c>
     </row>
@@ -11281,7 +12032,7 @@
       <c r="C111" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D111" s="19">
+      <c r="D111">
         <v>17830700</v>
       </c>
     </row>
@@ -11427,75 +12178,52 @@
       <c r="C117" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D117" s="19">
+      <c r="D117">
         <v>2240</v>
       </c>
-      <c r="E117" s="19">
+      <c r="E117">
         <v>560</v>
       </c>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19">
+      <c r="G117">
         <v>280</v>
       </c>
-      <c r="H117" s="19">
+      <c r="H117">
         <v>1970</v>
       </c>
-      <c r="I117" s="19">
+      <c r="I117">
         <v>2300</v>
       </c>
-      <c r="J117" s="19">
+      <c r="J117">
         <v>2300</v>
       </c>
-      <c r="K117" s="19">
+      <c r="K117">
         <v>1970</v>
       </c>
-      <c r="L117" s="19">
+      <c r="L117">
         <v>1970</v>
       </c>
-      <c r="M117" s="19">
+      <c r="M117">
         <v>1970</v>
       </c>
-      <c r="N117" s="19">
+      <c r="N117">
         <v>2300</v>
       </c>
-      <c r="O117" s="19">
+      <c r="O117">
         <v>2630</v>
       </c>
-      <c r="P117" s="19">
+      <c r="P117">
         <v>1970</v>
       </c>
-      <c r="Q117" s="19">
+      <c r="Q117">
         <v>1640</v>
       </c>
-      <c r="R117" s="19">
+      <c r="R117">
         <v>1970</v>
       </c>
-      <c r="S117" s="19">
+      <c r="S117">
         <v>1640</v>
       </c>
-      <c r="T117" s="19"/>
-      <c r="U117" s="19"/>
-      <c r="V117" s="19"/>
-      <c r="W117" s="19"/>
-      <c r="X117" s="19"/>
-      <c r="Y117" s="19"/>
-      <c r="Z117" s="19"/>
-      <c r="AA117" s="19"/>
-      <c r="AB117" s="19"/>
-      <c r="AC117" s="19"/>
-      <c r="AD117" s="19"/>
-      <c r="AE117" s="19"/>
-      <c r="AF117" s="19"/>
-      <c r="AG117" s="19"/>
-      <c r="AH117" s="19"/>
-      <c r="AI117" s="19"/>
-      <c r="AJ117" s="19"/>
-      <c r="AK117" s="19"/>
-      <c r="AL117" s="19"/>
-      <c r="AM117" s="19"/>
-      <c r="AN117" s="19"/>
-      <c r="AO117" s="19"/>
-      <c r="AP117" s="19">
+      <c r="AP117">
         <v>1847.3333333333333</v>
       </c>
     </row>
@@ -11503,77 +12231,55 @@
       <c r="C118" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D118" s="19"/>
-      <c r="E118" s="19"/>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="19">
+      <c r="H118">
         <v>2300</v>
       </c>
-      <c r="I118" s="19">
+      <c r="I118">
         <v>1970</v>
       </c>
-      <c r="J118" s="19">
+      <c r="J118">
         <v>2300</v>
       </c>
-      <c r="K118" s="19">
+      <c r="K118">
         <v>1970</v>
       </c>
-      <c r="L118" s="19">
+      <c r="L118">
         <v>1640</v>
       </c>
-      <c r="M118" s="19">
+      <c r="M118">
         <v>2300</v>
       </c>
-      <c r="N118" s="19">
+      <c r="N118">
         <v>1970</v>
       </c>
-      <c r="O118" s="19">
+      <c r="O118">
         <v>2630</v>
       </c>
-      <c r="P118" s="19"/>
-      <c r="Q118" s="19">
+      <c r="Q118">
         <v>1970</v>
       </c>
-      <c r="R118" s="19">
+      <c r="R118">
         <v>2300</v>
       </c>
-      <c r="S118" s="19"/>
-      <c r="T118" s="19">
+      <c r="T118">
         <v>1970</v>
       </c>
-      <c r="U118" s="19">
+      <c r="U118">
         <v>1970</v>
       </c>
-      <c r="V118" s="19">
+      <c r="V118">
         <v>1970</v>
       </c>
-      <c r="W118" s="19">
+      <c r="W118">
         <v>1970</v>
       </c>
-      <c r="X118" s="19">
+      <c r="X118">
         <v>1970</v>
       </c>
-      <c r="Y118" s="19">
+      <c r="Y118">
         <v>1970</v>
       </c>
-      <c r="Z118" s="19"/>
-      <c r="AA118" s="19"/>
-      <c r="AB118" s="19"/>
-      <c r="AC118" s="19"/>
-      <c r="AD118" s="19"/>
-      <c r="AE118" s="19"/>
-      <c r="AF118" s="19"/>
-      <c r="AG118" s="19"/>
-      <c r="AH118" s="19"/>
-      <c r="AI118" s="19"/>
-      <c r="AJ118" s="19"/>
-      <c r="AK118" s="19"/>
-      <c r="AL118" s="19"/>
-      <c r="AM118" s="19"/>
-      <c r="AN118" s="19"/>
-      <c r="AO118" s="19"/>
-      <c r="AP118" s="19">
+      <c r="AP118">
         <v>2073.125</v>
       </c>
     </row>
@@ -11581,51 +12287,16 @@
       <c r="C119" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D119" s="19">
+      <c r="D119">
         <v>300</v>
       </c>
-      <c r="E119" s="19"/>
-      <c r="F119" s="19">
+      <c r="F119">
         <v>100</v>
       </c>
-      <c r="G119" s="19">
+      <c r="G119">
         <v>350</v>
       </c>
-      <c r="H119" s="19"/>
-      <c r="I119" s="19"/>
-      <c r="J119" s="19"/>
-      <c r="K119" s="19"/>
-      <c r="L119" s="19"/>
-      <c r="M119" s="19"/>
-      <c r="N119" s="19"/>
-      <c r="O119" s="19"/>
-      <c r="P119" s="19"/>
-      <c r="Q119" s="19"/>
-      <c r="R119" s="19"/>
-      <c r="S119" s="19"/>
-      <c r="T119" s="19"/>
-      <c r="U119" s="19"/>
-      <c r="V119" s="19"/>
-      <c r="W119" s="19"/>
-      <c r="X119" s="19"/>
-      <c r="Y119" s="19"/>
-      <c r="Z119" s="19"/>
-      <c r="AA119" s="19"/>
-      <c r="AB119" s="19"/>
-      <c r="AC119" s="19"/>
-      <c r="AD119" s="19"/>
-      <c r="AE119" s="19"/>
-      <c r="AF119" s="19"/>
-      <c r="AG119" s="19"/>
-      <c r="AH119" s="19"/>
-      <c r="AI119" s="19"/>
-      <c r="AJ119" s="19"/>
-      <c r="AK119" s="19"/>
-      <c r="AL119" s="19"/>
-      <c r="AM119" s="19"/>
-      <c r="AN119" s="19"/>
-      <c r="AO119" s="19"/>
-      <c r="AP119" s="19">
+      <c r="AP119">
         <v>250</v>
       </c>
     </row>
@@ -11633,47 +12304,10 @@
       <c r="C120" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D120" s="19"/>
-      <c r="E120" s="19">
+      <c r="E120">
         <v>2500</v>
       </c>
-      <c r="F120" s="19"/>
-      <c r="G120" s="19"/>
-      <c r="H120" s="19"/>
-      <c r="I120" s="19"/>
-      <c r="J120" s="19"/>
-      <c r="K120" s="19"/>
-      <c r="L120" s="19"/>
-      <c r="M120" s="19"/>
-      <c r="N120" s="19"/>
-      <c r="O120" s="19"/>
-      <c r="P120" s="19"/>
-      <c r="Q120" s="19"/>
-      <c r="R120" s="19"/>
-      <c r="S120" s="19"/>
-      <c r="T120" s="19"/>
-      <c r="U120" s="19"/>
-      <c r="V120" s="19"/>
-      <c r="W120" s="19"/>
-      <c r="X120" s="19"/>
-      <c r="Y120" s="19"/>
-      <c r="Z120" s="19"/>
-      <c r="AA120" s="19"/>
-      <c r="AB120" s="19"/>
-      <c r="AC120" s="19"/>
-      <c r="AD120" s="19"/>
-      <c r="AE120" s="19"/>
-      <c r="AF120" s="19"/>
-      <c r="AG120" s="19"/>
-      <c r="AH120" s="19"/>
-      <c r="AI120" s="19"/>
-      <c r="AJ120" s="19"/>
-      <c r="AK120" s="19"/>
-      <c r="AL120" s="19"/>
-      <c r="AM120" s="19"/>
-      <c r="AN120" s="19"/>
-      <c r="AO120" s="19"/>
-      <c r="AP120" s="19">
+      <c r="AP120">
         <v>2500</v>
       </c>
     </row>
@@ -11681,47 +12315,10 @@
       <c r="C121" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D121" s="19"/>
-      <c r="E121" s="19"/>
-      <c r="F121" s="19"/>
-      <c r="G121" s="19">
+      <c r="G121">
         <v>1250</v>
       </c>
-      <c r="H121" s="19"/>
-      <c r="I121" s="19"/>
-      <c r="J121" s="19"/>
-      <c r="K121" s="19"/>
-      <c r="L121" s="19"/>
-      <c r="M121" s="19"/>
-      <c r="N121" s="19"/>
-      <c r="O121" s="19"/>
-      <c r="P121" s="19"/>
-      <c r="Q121" s="19"/>
-      <c r="R121" s="19"/>
-      <c r="S121" s="19"/>
-      <c r="T121" s="19"/>
-      <c r="U121" s="19"/>
-      <c r="V121" s="19"/>
-      <c r="W121" s="19"/>
-      <c r="X121" s="19"/>
-      <c r="Y121" s="19"/>
-      <c r="Z121" s="19"/>
-      <c r="AA121" s="19"/>
-      <c r="AB121" s="19"/>
-      <c r="AC121" s="19"/>
-      <c r="AD121" s="19"/>
-      <c r="AE121" s="19"/>
-      <c r="AF121" s="19"/>
-      <c r="AG121" s="19"/>
-      <c r="AH121" s="19"/>
-      <c r="AI121" s="19"/>
-      <c r="AJ121" s="19"/>
-      <c r="AK121" s="19"/>
-      <c r="AL121" s="19"/>
-      <c r="AM121" s="19"/>
-      <c r="AN121" s="19"/>
-      <c r="AO121" s="19"/>
-      <c r="AP121" s="19">
+      <c r="AP121">
         <v>1250</v>
       </c>
     </row>
@@ -11729,49 +12326,13 @@
       <c r="C122" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D122" s="19"/>
-      <c r="E122" s="19"/>
-      <c r="F122" s="19">
+      <c r="F122">
         <v>1260</v>
       </c>
-      <c r="G122" s="19">
+      <c r="G122">
         <v>1260</v>
       </c>
-      <c r="H122" s="19"/>
-      <c r="I122" s="19"/>
-      <c r="J122" s="19"/>
-      <c r="K122" s="19"/>
-      <c r="L122" s="19"/>
-      <c r="M122" s="19"/>
-      <c r="N122" s="19"/>
-      <c r="O122" s="19"/>
-      <c r="P122" s="19"/>
-      <c r="Q122" s="19"/>
-      <c r="R122" s="19"/>
-      <c r="S122" s="19"/>
-      <c r="T122" s="19"/>
-      <c r="U122" s="19"/>
-      <c r="V122" s="19"/>
-      <c r="W122" s="19"/>
-      <c r="X122" s="19"/>
-      <c r="Y122" s="19"/>
-      <c r="Z122" s="19"/>
-      <c r="AA122" s="19"/>
-      <c r="AB122" s="19"/>
-      <c r="AC122" s="19"/>
-      <c r="AD122" s="19"/>
-      <c r="AE122" s="19"/>
-      <c r="AF122" s="19"/>
-      <c r="AG122" s="19"/>
-      <c r="AH122" s="19"/>
-      <c r="AI122" s="19"/>
-      <c r="AJ122" s="19"/>
-      <c r="AK122" s="19"/>
-      <c r="AL122" s="19"/>
-      <c r="AM122" s="19"/>
-      <c r="AN122" s="19"/>
-      <c r="AO122" s="19"/>
-      <c r="AP122" s="19">
+      <c r="AP122">
         <v>1260</v>
       </c>
     </row>
@@ -11779,49 +12340,13 @@
       <c r="C123" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D123" s="19"/>
-      <c r="E123" s="19"/>
-      <c r="F123" s="19">
+      <c r="F123">
         <v>1440</v>
       </c>
-      <c r="G123" s="19">
+      <c r="G123">
         <v>1440</v>
       </c>
-      <c r="H123" s="19"/>
-      <c r="I123" s="19"/>
-      <c r="J123" s="19"/>
-      <c r="K123" s="19"/>
-      <c r="L123" s="19"/>
-      <c r="M123" s="19"/>
-      <c r="N123" s="19"/>
-      <c r="O123" s="19"/>
-      <c r="P123" s="19"/>
-      <c r="Q123" s="19"/>
-      <c r="R123" s="19"/>
-      <c r="S123" s="19"/>
-      <c r="T123" s="19"/>
-      <c r="U123" s="19"/>
-      <c r="V123" s="19"/>
-      <c r="W123" s="19"/>
-      <c r="X123" s="19"/>
-      <c r="Y123" s="19"/>
-      <c r="Z123" s="19"/>
-      <c r="AA123" s="19"/>
-      <c r="AB123" s="19"/>
-      <c r="AC123" s="19"/>
-      <c r="AD123" s="19"/>
-      <c r="AE123" s="19"/>
-      <c r="AF123" s="19"/>
-      <c r="AG123" s="19"/>
-      <c r="AH123" s="19"/>
-      <c r="AI123" s="19"/>
-      <c r="AJ123" s="19"/>
-      <c r="AK123" s="19"/>
-      <c r="AL123" s="19"/>
-      <c r="AM123" s="19"/>
-      <c r="AN123" s="19"/>
-      <c r="AO123" s="19"/>
-      <c r="AP123" s="19">
+      <c r="AP123">
         <v>1440</v>
       </c>
     </row>
@@ -11829,51 +12354,16 @@
       <c r="C124" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D124" s="19">
+      <c r="D124">
         <v>360</v>
       </c>
-      <c r="E124" s="19"/>
-      <c r="F124" s="19">
+      <c r="F124">
         <v>120</v>
       </c>
-      <c r="G124" s="19">
+      <c r="G124">
         <v>840</v>
       </c>
-      <c r="H124" s="19"/>
-      <c r="I124" s="19"/>
-      <c r="J124" s="19"/>
-      <c r="K124" s="19"/>
-      <c r="L124" s="19"/>
-      <c r="M124" s="19"/>
-      <c r="N124" s="19"/>
-      <c r="O124" s="19"/>
-      <c r="P124" s="19"/>
-      <c r="Q124" s="19"/>
-      <c r="R124" s="19"/>
-      <c r="S124" s="19"/>
-      <c r="T124" s="19"/>
-      <c r="U124" s="19"/>
-      <c r="V124" s="19"/>
-      <c r="W124" s="19"/>
-      <c r="X124" s="19"/>
-      <c r="Y124" s="19"/>
-      <c r="Z124" s="19"/>
-      <c r="AA124" s="19"/>
-      <c r="AB124" s="19"/>
-      <c r="AC124" s="19"/>
-      <c r="AD124" s="19"/>
-      <c r="AE124" s="19"/>
-      <c r="AF124" s="19"/>
-      <c r="AG124" s="19"/>
-      <c r="AH124" s="19"/>
-      <c r="AI124" s="19"/>
-      <c r="AJ124" s="19"/>
-      <c r="AK124" s="19"/>
-      <c r="AL124" s="19"/>
-      <c r="AM124" s="19"/>
-      <c r="AN124" s="19"/>
-      <c r="AO124" s="19"/>
-      <c r="AP124" s="19">
+      <c r="AP124">
         <v>440</v>
       </c>
     </row>
@@ -11881,53 +12371,19 @@
       <c r="C125" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D125" s="19">
+      <c r="D125">
         <v>1560</v>
       </c>
-      <c r="E125" s="19">
+      <c r="E125">
         <v>1200</v>
       </c>
-      <c r="F125" s="19">
+      <c r="F125">
         <v>480</v>
       </c>
-      <c r="G125" s="19">
+      <c r="G125">
         <v>480</v>
       </c>
-      <c r="H125" s="19"/>
-      <c r="I125" s="19"/>
-      <c r="J125" s="19"/>
-      <c r="K125" s="19"/>
-      <c r="L125" s="19"/>
-      <c r="M125" s="19"/>
-      <c r="N125" s="19"/>
-      <c r="O125" s="19"/>
-      <c r="P125" s="19"/>
-      <c r="Q125" s="19"/>
-      <c r="R125" s="19"/>
-      <c r="S125" s="19"/>
-      <c r="T125" s="19"/>
-      <c r="U125" s="19"/>
-      <c r="V125" s="19"/>
-      <c r="W125" s="19"/>
-      <c r="X125" s="19"/>
-      <c r="Y125" s="19"/>
-      <c r="Z125" s="19"/>
-      <c r="AA125" s="19"/>
-      <c r="AB125" s="19"/>
-      <c r="AC125" s="19"/>
-      <c r="AD125" s="19"/>
-      <c r="AE125" s="19"/>
-      <c r="AF125" s="19"/>
-      <c r="AG125" s="19"/>
-      <c r="AH125" s="19"/>
-      <c r="AI125" s="19"/>
-      <c r="AJ125" s="19"/>
-      <c r="AK125" s="19"/>
-      <c r="AL125" s="19"/>
-      <c r="AM125" s="19"/>
-      <c r="AN125" s="19"/>
-      <c r="AO125" s="19"/>
-      <c r="AP125" s="19">
+      <c r="AP125">
         <v>930</v>
       </c>
     </row>
@@ -11935,65 +12391,37 @@
       <c r="C126" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D126" s="19"/>
-      <c r="E126" s="19"/>
-      <c r="F126" s="19"/>
-      <c r="G126" s="19"/>
-      <c r="H126" s="19"/>
-      <c r="I126" s="19">
+      <c r="I126">
         <v>3520</v>
       </c>
-      <c r="J126" s="19"/>
-      <c r="K126" s="19"/>
-      <c r="L126" s="19">
+      <c r="L126">
         <v>4230</v>
       </c>
-      <c r="M126" s="19"/>
-      <c r="N126" s="19"/>
-      <c r="O126" s="19">
+      <c r="O126">
         <v>3520</v>
       </c>
-      <c r="P126" s="19"/>
-      <c r="Q126" s="19"/>
-      <c r="R126" s="19">
+      <c r="R126">
         <v>4230</v>
       </c>
-      <c r="S126" s="19"/>
-      <c r="T126" s="19">
+      <c r="T126">
         <v>4930</v>
       </c>
-      <c r="U126" s="19">
+      <c r="U126">
         <v>4230</v>
       </c>
-      <c r="V126" s="19">
+      <c r="V126">
         <v>3520</v>
       </c>
-      <c r="W126" s="19">
+      <c r="W126">
         <v>3520</v>
       </c>
-      <c r="X126" s="19">
+      <c r="X126">
         <v>4230</v>
       </c>
-      <c r="Y126" s="19">
+      <c r="Y126">
         <v>4230</v>
       </c>
-      <c r="Z126" s="19"/>
-      <c r="AA126" s="19"/>
-      <c r="AB126" s="19"/>
-      <c r="AC126" s="19"/>
-      <c r="AD126" s="19"/>
-      <c r="AE126" s="19"/>
-      <c r="AF126" s="19"/>
-      <c r="AG126" s="19"/>
-      <c r="AH126" s="19"/>
-      <c r="AI126" s="19"/>
-      <c r="AJ126" s="19"/>
-      <c r="AK126" s="19"/>
-      <c r="AL126" s="19"/>
-      <c r="AM126" s="19"/>
-      <c r="AN126" s="19"/>
-      <c r="AO126" s="19"/>
-      <c r="AP126" s="19">
+      <c r="AP126">
         <v>4016</v>
       </c>
     </row>
@@ -12001,53 +12429,19 @@
       <c r="C127" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D127" s="19"/>
-      <c r="E127" s="19"/>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
-      <c r="H127" s="19"/>
-      <c r="I127" s="19"/>
-      <c r="J127" s="19"/>
-      <c r="K127" s="19"/>
-      <c r="L127" s="19"/>
-      <c r="M127" s="19"/>
-      <c r="N127" s="19"/>
-      <c r="O127" s="19"/>
-      <c r="P127" s="19">
+      <c r="P127">
         <v>1410</v>
       </c>
-      <c r="Q127" s="19"/>
-      <c r="R127" s="19"/>
-      <c r="S127" s="19">
+      <c r="S127">
         <v>1880</v>
       </c>
-      <c r="T127" s="19"/>
-      <c r="U127" s="19">
+      <c r="U127">
         <v>1410</v>
       </c>
-      <c r="V127" s="19"/>
-      <c r="W127" s="19"/>
-      <c r="X127" s="19">
+      <c r="X127">
         <v>1880</v>
       </c>
-      <c r="Y127" s="19"/>
-      <c r="Z127" s="19"/>
-      <c r="AA127" s="19"/>
-      <c r="AB127" s="19"/>
-      <c r="AC127" s="19"/>
-      <c r="AD127" s="19"/>
-      <c r="AE127" s="19"/>
-      <c r="AF127" s="19"/>
-      <c r="AG127" s="19"/>
-      <c r="AH127" s="19"/>
-      <c r="AI127" s="19"/>
-      <c r="AJ127" s="19"/>
-      <c r="AK127" s="19"/>
-      <c r="AL127" s="19"/>
-      <c r="AM127" s="19"/>
-      <c r="AN127" s="19"/>
-      <c r="AO127" s="19"/>
-      <c r="AP127" s="19">
+      <c r="AP127">
         <v>1645</v>
       </c>
     </row>
@@ -12055,47 +12449,10 @@
       <c r="C128" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19">
+      <c r="F128">
         <v>360</v>
       </c>
-      <c r="G128" s="19"/>
-      <c r="H128" s="19"/>
-      <c r="I128" s="19"/>
-      <c r="J128" s="19"/>
-      <c r="K128" s="19"/>
-      <c r="L128" s="19"/>
-      <c r="M128" s="19"/>
-      <c r="N128" s="19"/>
-      <c r="O128" s="19"/>
-      <c r="P128" s="19"/>
-      <c r="Q128" s="19"/>
-      <c r="R128" s="19"/>
-      <c r="S128" s="19"/>
-      <c r="T128" s="19"/>
-      <c r="U128" s="19"/>
-      <c r="V128" s="19"/>
-      <c r="W128" s="19"/>
-      <c r="X128" s="19"/>
-      <c r="Y128" s="19"/>
-      <c r="Z128" s="19"/>
-      <c r="AA128" s="19"/>
-      <c r="AB128" s="19"/>
-      <c r="AC128" s="19"/>
-      <c r="AD128" s="19"/>
-      <c r="AE128" s="19"/>
-      <c r="AF128" s="19"/>
-      <c r="AG128" s="19"/>
-      <c r="AH128" s="19"/>
-      <c r="AI128" s="19"/>
-      <c r="AJ128" s="19"/>
-      <c r="AK128" s="19"/>
-      <c r="AL128" s="19"/>
-      <c r="AM128" s="19"/>
-      <c r="AN128" s="19"/>
-      <c r="AO128" s="19"/>
-      <c r="AP128" s="19">
+      <c r="AP128">
         <v>360</v>
       </c>
     </row>
@@ -12103,53 +12460,19 @@
       <c r="C129" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D129" s="19"/>
-      <c r="E129" s="19"/>
-      <c r="F129" s="19"/>
-      <c r="G129" s="19"/>
-      <c r="H129" s="19"/>
-      <c r="I129" s="19"/>
-      <c r="J129" s="19"/>
-      <c r="K129" s="19"/>
-      <c r="L129" s="19"/>
-      <c r="M129" s="19"/>
-      <c r="N129" s="19"/>
-      <c r="O129" s="19"/>
-      <c r="P129" s="19"/>
-      <c r="Q129" s="19"/>
-      <c r="R129" s="19"/>
-      <c r="S129" s="19"/>
-      <c r="T129" s="19"/>
-      <c r="U129" s="19"/>
-      <c r="V129" s="19"/>
-      <c r="W129" s="19"/>
-      <c r="X129" s="19"/>
-      <c r="Y129" s="19"/>
-      <c r="Z129" s="19"/>
-      <c r="AA129" s="19"/>
-      <c r="AB129" s="19">
+      <c r="AB129">
         <v>950</v>
       </c>
-      <c r="AC129" s="19"/>
-      <c r="AD129" s="19">
+      <c r="AD129">
         <v>600</v>
       </c>
-      <c r="AE129" s="19"/>
-      <c r="AF129" s="19"/>
-      <c r="AG129" s="19"/>
-      <c r="AH129" s="19"/>
-      <c r="AI129" s="19"/>
-      <c r="AJ129" s="19"/>
-      <c r="AK129" s="19"/>
-      <c r="AL129" s="19">
+      <c r="AL129">
         <v>850</v>
       </c>
-      <c r="AM129" s="19"/>
-      <c r="AN129" s="19"/>
-      <c r="AO129" s="19">
+      <c r="AO129">
         <v>800</v>
       </c>
-      <c r="AP129" s="19">
+      <c r="AP129">
         <v>800</v>
       </c>
     </row>
@@ -12157,63 +12480,34 @@
       <c r="C130" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D130" s="19"/>
-      <c r="E130" s="19"/>
-      <c r="F130" s="19"/>
-      <c r="G130" s="19"/>
-      <c r="H130" s="19"/>
-      <c r="I130" s="19"/>
-      <c r="J130" s="19"/>
-      <c r="K130" s="19"/>
-      <c r="L130" s="19"/>
-      <c r="M130" s="19"/>
-      <c r="N130" s="19"/>
-      <c r="O130" s="19"/>
-      <c r="P130" s="19"/>
-      <c r="Q130" s="19"/>
-      <c r="R130" s="19"/>
-      <c r="S130" s="19"/>
-      <c r="T130" s="19"/>
-      <c r="U130" s="19"/>
-      <c r="V130" s="19"/>
-      <c r="W130" s="19"/>
-      <c r="X130" s="19"/>
-      <c r="Y130" s="19"/>
-      <c r="Z130" s="19"/>
-      <c r="AA130" s="19">
+      <c r="AA130">
         <v>1400</v>
       </c>
-      <c r="AB130" s="19"/>
-      <c r="AC130" s="19"/>
-      <c r="AD130" s="19">
+      <c r="AD130">
         <v>1600</v>
       </c>
-      <c r="AE130" s="19"/>
-      <c r="AF130" s="19">
+      <c r="AF130">
         <v>1200</v>
       </c>
-      <c r="AG130" s="19"/>
-      <c r="AH130" s="19"/>
-      <c r="AI130" s="19">
+      <c r="AI130">
         <v>1000</v>
       </c>
-      <c r="AJ130" s="19"/>
-      <c r="AK130" s="19">
+      <c r="AK130">
         <v>1300</v>
       </c>
-      <c r="AL130" s="19">
+      <c r="AL130">
         <v>1400</v>
       </c>
-      <c r="AM130" s="19">
+      <c r="AM130">
         <v>1400</v>
       </c>
-      <c r="AN130" s="19">
+      <c r="AN130">
         <v>1200</v>
       </c>
-      <c r="AO130" s="19">
+      <c r="AO130">
         <v>1900</v>
       </c>
-      <c r="AP130" s="19">
+      <c r="AP130">
         <v>1430</v>
       </c>
     </row>
@@ -12221,75 +12515,52 @@
       <c r="C131" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D131" s="19"/>
-      <c r="E131" s="19"/>
-      <c r="F131" s="19"/>
-      <c r="G131" s="19"/>
-      <c r="H131" s="19"/>
-      <c r="I131" s="19"/>
-      <c r="J131" s="19"/>
-      <c r="K131" s="19"/>
-      <c r="L131" s="19"/>
-      <c r="M131" s="19"/>
-      <c r="N131" s="19"/>
-      <c r="O131" s="19"/>
-      <c r="P131" s="19"/>
-      <c r="Q131" s="19"/>
-      <c r="R131" s="19"/>
-      <c r="S131" s="19"/>
-      <c r="T131" s="19"/>
-      <c r="U131" s="19"/>
-      <c r="V131" s="19"/>
-      <c r="W131" s="19"/>
-      <c r="X131" s="19"/>
-      <c r="Y131" s="19"/>
-      <c r="Z131" s="19">
+      <c r="Z131">
         <v>1920</v>
       </c>
-      <c r="AA131" s="19">
+      <c r="AA131">
         <v>1560</v>
       </c>
-      <c r="AB131" s="19"/>
-      <c r="AC131" s="19">
+      <c r="AC131">
         <v>1320</v>
       </c>
-      <c r="AD131" s="19">
+      <c r="AD131">
         <v>1680</v>
       </c>
-      <c r="AE131" s="19">
+      <c r="AE131">
         <v>1680</v>
       </c>
-      <c r="AF131" s="19">
+      <c r="AF131">
         <v>1560</v>
       </c>
-      <c r="AG131" s="19">
+      <c r="AG131">
         <v>1680</v>
       </c>
-      <c r="AH131" s="19">
+      <c r="AH131">
         <v>1800</v>
       </c>
-      <c r="AI131" s="19">
+      <c r="AI131">
         <v>1800</v>
       </c>
-      <c r="AJ131" s="19">
+      <c r="AJ131">
         <v>1680</v>
       </c>
-      <c r="AK131" s="19">
+      <c r="AK131">
         <v>1680</v>
       </c>
-      <c r="AL131" s="19">
+      <c r="AL131">
         <v>1440</v>
       </c>
-      <c r="AM131" s="19">
+      <c r="AM131">
         <v>2280</v>
       </c>
-      <c r="AN131" s="19">
+      <c r="AN131">
         <v>2160</v>
       </c>
-      <c r="AO131" s="19">
+      <c r="AO131">
         <v>1860</v>
       </c>
-      <c r="AP131" s="19">
+      <c r="AP131">
         <v>1747.5</v>
       </c>
     </row>
@@ -12297,67 +12568,40 @@
       <c r="C132" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D132" s="19"/>
-      <c r="E132" s="19"/>
-      <c r="F132" s="19"/>
-      <c r="G132" s="19"/>
-      <c r="H132" s="19"/>
-      <c r="I132" s="19"/>
-      <c r="J132" s="19"/>
-      <c r="K132" s="19"/>
-      <c r="L132" s="19"/>
-      <c r="M132" s="19"/>
-      <c r="N132" s="19"/>
-      <c r="O132" s="19"/>
-      <c r="P132" s="19"/>
-      <c r="Q132" s="19"/>
-      <c r="R132" s="19"/>
-      <c r="S132" s="19"/>
-      <c r="T132" s="19"/>
-      <c r="U132" s="19"/>
-      <c r="V132" s="19"/>
-      <c r="W132" s="19"/>
-      <c r="X132" s="19"/>
-      <c r="Y132" s="19"/>
-      <c r="Z132" s="19">
+      <c r="Z132">
         <v>1680</v>
       </c>
-      <c r="AA132" s="19">
+      <c r="AA132">
         <v>2280</v>
       </c>
-      <c r="AB132" s="19">
+      <c r="AB132">
         <v>1440</v>
       </c>
-      <c r="AC132" s="19">
+      <c r="AC132">
         <v>1440</v>
       </c>
-      <c r="AD132" s="19">
+      <c r="AD132">
         <v>1920</v>
       </c>
-      <c r="AE132" s="19">
+      <c r="AE132">
         <v>1680</v>
       </c>
-      <c r="AF132" s="19">
+      <c r="AF132">
         <v>1440</v>
       </c>
-      <c r="AG132" s="19">
+      <c r="AG132">
         <v>1680</v>
       </c>
-      <c r="AH132" s="19">
+      <c r="AH132">
         <v>1440</v>
       </c>
-      <c r="AI132" s="19">
+      <c r="AI132">
         <v>1680</v>
       </c>
-      <c r="AJ132" s="19">
+      <c r="AJ132">
         <v>2040</v>
       </c>
-      <c r="AK132" s="19"/>
-      <c r="AL132" s="19"/>
-      <c r="AM132" s="19"/>
-      <c r="AN132" s="19"/>
-      <c r="AO132" s="19"/>
-      <c r="AP132" s="19">
+      <c r="AP132">
         <v>1720</v>
       </c>
     </row>
@@ -12365,121 +12609,121 @@
       <c r="C133" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D133" s="19">
+      <c r="D133">
         <v>1115</v>
       </c>
-      <c r="E133" s="19">
+      <c r="E133">
         <v>1420</v>
       </c>
-      <c r="F133" s="19">
+      <c r="F133">
         <v>717.14285714285711</v>
       </c>
-      <c r="G133" s="19">
+      <c r="G133">
         <v>842.85714285714289</v>
       </c>
-      <c r="H133" s="19">
+      <c r="H133">
         <v>2135</v>
       </c>
-      <c r="I133" s="19">
+      <c r="I133">
         <v>2596.6666666666665</v>
       </c>
-      <c r="J133" s="19">
+      <c r="J133">
         <v>2300</v>
       </c>
-      <c r="K133" s="19">
+      <c r="K133">
         <v>1970</v>
       </c>
-      <c r="L133" s="19">
+      <c r="L133">
         <v>2613.3333333333335</v>
       </c>
-      <c r="M133" s="19">
+      <c r="M133">
         <v>2135</v>
       </c>
-      <c r="N133" s="19">
+      <c r="N133">
         <v>2135</v>
       </c>
-      <c r="O133" s="19">
+      <c r="O133">
         <v>2926.6666666666665</v>
       </c>
-      <c r="P133" s="19">
+      <c r="P133">
         <v>1690</v>
       </c>
-      <c r="Q133" s="19">
+      <c r="Q133">
         <v>1805</v>
       </c>
-      <c r="R133" s="19">
+      <c r="R133">
         <v>2833.3333333333335</v>
       </c>
-      <c r="S133" s="19">
+      <c r="S133">
         <v>1760</v>
       </c>
-      <c r="T133" s="19">
+      <c r="T133">
         <v>3450</v>
       </c>
-      <c r="U133" s="19">
+      <c r="U133">
         <v>2536.6666666666665</v>
       </c>
-      <c r="V133" s="19">
+      <c r="V133">
         <v>2745</v>
       </c>
-      <c r="W133" s="19">
+      <c r="W133">
         <v>2745</v>
       </c>
-      <c r="X133" s="19">
+      <c r="X133">
         <v>2693.3333333333335</v>
       </c>
-      <c r="Y133" s="19">
+      <c r="Y133">
         <v>3100</v>
       </c>
-      <c r="Z133" s="19">
+      <c r="Z133">
         <v>1800</v>
       </c>
-      <c r="AA133" s="19">
+      <c r="AA133">
         <v>1746.6666666666667</v>
       </c>
-      <c r="AB133" s="19">
+      <c r="AB133">
         <v>1195</v>
       </c>
-      <c r="AC133" s="19">
+      <c r="AC133">
         <v>1380</v>
       </c>
-      <c r="AD133" s="19">
+      <c r="AD133">
         <v>1544</v>
       </c>
-      <c r="AE133" s="19">
+      <c r="AE133">
         <v>1680</v>
       </c>
-      <c r="AF133" s="19">
+      <c r="AF133">
         <v>1400</v>
       </c>
-      <c r="AG133" s="19">
+      <c r="AG133">
         <v>1680</v>
       </c>
-      <c r="AH133" s="19">
+      <c r="AH133">
         <v>1620</v>
       </c>
-      <c r="AI133" s="19">
+      <c r="AI133">
         <v>1493.3333333333333</v>
       </c>
-      <c r="AJ133" s="19">
+      <c r="AJ133">
         <v>1860</v>
       </c>
-      <c r="AK133" s="19">
+      <c r="AK133">
         <v>1490</v>
       </c>
-      <c r="AL133" s="19">
+      <c r="AL133">
         <v>1230</v>
       </c>
-      <c r="AM133" s="19">
+      <c r="AM133">
         <v>1840</v>
       </c>
-      <c r="AN133" s="19">
+      <c r="AN133">
         <v>1680</v>
       </c>
-      <c r="AO133" s="19">
+      <c r="AO133">
         <v>1664</v>
       </c>
-      <c r="AP133" s="19">
+      <c r="AP133">
         <v>1812.1904761904761</v>
       </c>
     </row>
@@ -12489,6 +12733,955 @@
       </c>
       <c r="C136" s="17" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="137" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="C137" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D137" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="138" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="C138" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D138">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="C139" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="C140" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="141" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="C141" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D141">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="C142" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D142">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="B146" s="6">
+        <v>10</v>
+      </c>
+      <c r="C146" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C147" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D147" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C148" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D148" s="20">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C149" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" s="20">
+        <v>124.82758620689656</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C150" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="20">
+        <v>110.58823529411765</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C151" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D151" s="20">
+        <v>63.18181818181818</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C152" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D152">
+        <v>95.142857142857139</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="B155" s="6">
+        <v>11</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C156" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D156" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C157" s="19">
+        <v>43983</v>
+      </c>
+      <c r="D157">
+        <v>1312200</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C158" s="19">
+        <v>43984</v>
+      </c>
+      <c r="D158">
+        <v>1320000</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C159" s="19">
+        <v>43985</v>
+      </c>
+      <c r="D159">
+        <v>253200</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C160" s="19">
+        <v>43986</v>
+      </c>
+      <c r="D160">
+        <v>435200</v>
+      </c>
+    </row>
+    <row r="161" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C161" s="19">
+        <v>43987</v>
+      </c>
+      <c r="D161">
+        <v>192000</v>
+      </c>
+    </row>
+    <row r="162" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C162" s="19">
+        <v>43988</v>
+      </c>
+      <c r="D162">
+        <v>491200</v>
+      </c>
+    </row>
+    <row r="163" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C163" s="19">
+        <v>43989</v>
+      </c>
+      <c r="D163">
+        <v>603800</v>
+      </c>
+    </row>
+    <row r="164" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C164" s="19">
+        <v>43990</v>
+      </c>
+      <c r="D164">
+        <v>805900</v>
+      </c>
+    </row>
+    <row r="165" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C165" s="19">
+        <v>43991</v>
+      </c>
+      <c r="D165">
+        <v>846800</v>
+      </c>
+    </row>
+    <row r="166" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C166" s="19">
+        <v>43992</v>
+      </c>
+      <c r="D166">
+        <v>564000</v>
+      </c>
+    </row>
+    <row r="167" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C167" s="19">
+        <v>43993</v>
+      </c>
+      <c r="D167">
+        <v>620700</v>
+      </c>
+    </row>
+    <row r="168" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C168" s="19">
+        <v>43994</v>
+      </c>
+      <c r="D168">
+        <v>516400</v>
+      </c>
+    </row>
+    <row r="169" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C169" s="19">
+        <v>43995</v>
+      </c>
+      <c r="D169">
+        <v>657600</v>
+      </c>
+    </row>
+    <row r="170" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C170" s="19">
+        <v>43996</v>
+      </c>
+      <c r="D170">
+        <v>622000</v>
+      </c>
+    </row>
+    <row r="171" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C171" s="19">
+        <v>43997</v>
+      </c>
+      <c r="D171">
+        <v>1365800</v>
+      </c>
+    </row>
+    <row r="172" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C172" s="19">
+        <v>43998</v>
+      </c>
+      <c r="D172">
+        <v>1537400</v>
+      </c>
+    </row>
+    <row r="173" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C173" s="19">
+        <v>43999</v>
+      </c>
+      <c r="D173">
+        <v>643200</v>
+      </c>
+    </row>
+    <row r="174" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C174" s="19">
+        <v>44000</v>
+      </c>
+      <c r="D174">
+        <v>852400</v>
+      </c>
+    </row>
+    <row r="175" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C175" s="19">
+        <v>44001</v>
+      </c>
+      <c r="D175">
+        <v>1037800</v>
+      </c>
+    </row>
+    <row r="176" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C176" s="19">
+        <v>44002</v>
+      </c>
+      <c r="D176">
+        <v>579000</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C177" s="19">
+        <v>44003</v>
+      </c>
+      <c r="D177">
+        <v>459900</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C178" s="19">
+        <v>44004</v>
+      </c>
+      <c r="D178">
+        <v>390900</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C179" s="19">
+        <v>44005</v>
+      </c>
+      <c r="D179">
+        <v>720200</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C180" s="19">
+        <v>44006</v>
+      </c>
+      <c r="D180">
+        <v>176000</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C181" s="19">
+        <v>44007</v>
+      </c>
+      <c r="D181">
+        <v>245600</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C182" s="19">
+        <v>44008</v>
+      </c>
+      <c r="D182">
+        <v>118200</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C183" s="19">
+        <v>44011</v>
+      </c>
+      <c r="D183">
+        <v>118200</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C184" s="19">
+        <v>44012</v>
+      </c>
+      <c r="D184">
+        <v>345100</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C185" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D185">
+        <v>17830700</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="B188" s="6">
+        <v>12</v>
+      </c>
+      <c r="C188" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C189" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D189" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C190" s="9">
+        <v>65666</v>
+      </c>
+      <c r="D190">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C191" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D191">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="B195" s="6">
+        <v>13</v>
+      </c>
+      <c r="C195" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C196" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D196" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C197" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D197" t="s">
+        <v>21</v>
+      </c>
+      <c r="E197" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C198" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D198">
+        <v>110</v>
+      </c>
+      <c r="E198">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C199" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D199">
+        <v>130</v>
+      </c>
+      <c r="E199">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C200" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D200">
+        <v>100</v>
+      </c>
+      <c r="E200">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C201" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D201">
+        <v>50</v>
+      </c>
+      <c r="E201">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="202" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C202" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D202">
+        <v>70</v>
+      </c>
+      <c r="E202">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C203" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D203">
+        <v>80</v>
+      </c>
+      <c r="E203">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C204" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D204">
+        <v>100</v>
+      </c>
+      <c r="E204">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C205" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D205">
+        <v>270</v>
+      </c>
+      <c r="E205">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C206" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D206">
+        <v>640</v>
+      </c>
+      <c r="E206">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C207" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D207">
+        <v>550</v>
+      </c>
+      <c r="E207">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208">
+        <v>820</v>
+      </c>
+      <c r="E208">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C209" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D209">
+        <v>840</v>
+      </c>
+      <c r="E209">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C210" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D210">
+        <v>3760</v>
+      </c>
+      <c r="E210">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="B214" s="6">
+        <v>14</v>
+      </c>
+      <c r="C214" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="215" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C215" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D215" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C216" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D216" t="s">
+        <v>12</v>
+      </c>
+      <c r="E216" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="217" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C217" s="9">
+        <v>65627</v>
+      </c>
+      <c r="D217" s="20">
+        <v>1800</v>
+      </c>
+      <c r="E217" s="20">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C218" s="9">
+        <v>65629</v>
+      </c>
+      <c r="D218" s="20">
+        <v>1746.6666666666667</v>
+      </c>
+      <c r="E218" s="20">
+        <v>1746.6666666666667</v>
+      </c>
+    </row>
+    <row r="219" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C219" s="9">
+        <v>65631</v>
+      </c>
+      <c r="D219" s="20">
+        <v>1195</v>
+      </c>
+      <c r="E219" s="20">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="220" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C220" s="9">
+        <v>65662</v>
+      </c>
+      <c r="D220" s="20">
+        <v>1380</v>
+      </c>
+      <c r="E220" s="20">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="221" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C221" s="9">
+        <v>65666</v>
+      </c>
+      <c r="D221" s="20">
+        <v>1544</v>
+      </c>
+      <c r="E221" s="20">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="222" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C222" s="9">
+        <v>66015</v>
+      </c>
+      <c r="D222" s="20">
+        <v>1680</v>
+      </c>
+      <c r="E222" s="20">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="223" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C223" s="9">
+        <v>66016</v>
+      </c>
+      <c r="D223" s="20">
+        <v>1400</v>
+      </c>
+      <c r="E223" s="20">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="224" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C224" s="9">
+        <v>66017</v>
+      </c>
+      <c r="D224" s="20">
+        <v>1680</v>
+      </c>
+      <c r="E224" s="20">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="225" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C225" s="9">
+        <v>66030</v>
+      </c>
+      <c r="D225" s="20">
+        <v>1620</v>
+      </c>
+      <c r="E225" s="20">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C226" s="9">
+        <v>66031</v>
+      </c>
+      <c r="D226" s="20">
+        <v>1493.3333333333333</v>
+      </c>
+      <c r="E226" s="20">
+        <v>1493.3333333333333</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C227" s="9">
+        <v>66032</v>
+      </c>
+      <c r="D227" s="20">
+        <v>1860</v>
+      </c>
+      <c r="E227" s="20">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C228" s="9">
+        <v>68097</v>
+      </c>
+      <c r="D228" s="20">
+        <v>1490</v>
+      </c>
+      <c r="E228" s="20">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C229" s="9">
+        <v>68099</v>
+      </c>
+      <c r="D229" s="20">
+        <v>1230</v>
+      </c>
+      <c r="E229" s="20">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C230" s="9">
+        <v>68101</v>
+      </c>
+      <c r="D230" s="20">
+        <v>1840</v>
+      </c>
+      <c r="E230" s="20">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="231" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C231" s="9">
+        <v>68112</v>
+      </c>
+      <c r="D231" s="20">
+        <v>1680</v>
+      </c>
+      <c r="E231" s="20">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C232" s="9">
+        <v>68116</v>
+      </c>
+      <c r="D232" s="20">
+        <v>1664</v>
+      </c>
+      <c r="E232" s="20">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="233" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C233" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D233">
+        <v>1573.8095238095239</v>
+      </c>
+      <c r="E233">
+        <v>1573.8095238095239</v>
+      </c>
+    </row>
+    <row r="237" spans="2:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="B237" s="6">
+        <v>15</v>
+      </c>
+      <c r="C237" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="238" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C238" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D238" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="239" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C239" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D239" t="s">
+        <v>13</v>
+      </c>
+      <c r="E239" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="240" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C240" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D240">
+        <v>3</v>
+      </c>
+      <c r="E240">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C241" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D241">
+        <v>3</v>
+      </c>
+      <c r="E241">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C242" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C243" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D243">
+        <v>1</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C244" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D244">
+        <v>3</v>
+      </c>
+      <c r="E244">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C245" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D245">
+        <v>2</v>
+      </c>
+      <c r="E245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C246" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D246">
+        <v>3</v>
+      </c>
+      <c r="E246">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C247" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D247">
+        <v>4</v>
+      </c>
+      <c r="E247">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C248" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D248">
+        <v>1</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C249" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D249">
+        <v>4</v>
+      </c>
+      <c r="E249">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C250" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D250">
+        <v>10</v>
+      </c>
+      <c r="E250">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C251" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D251">
+        <v>16</v>
+      </c>
+      <c r="E251">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C252" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D252">
+        <v>12</v>
+      </c>
+      <c r="E252">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C253" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D253">
+        <v>63</v>
+      </c>
+      <c r="E253">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Case Study 2(Pivot Table).xlsx
+++ b/Excel/Case Study 2(Pivot Table).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068B62D8-CBAF-4FD6-9CE5-818E153B6F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEAA80E-B1C6-4D12-ADAF-A789CDDAF2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C2F27DB-59A7-4E77-BCCC-EA28361B83B3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3C2F27DB-59A7-4E77-BCCC-EA28361B83B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId4"/>
-    <pivotCache cacheId="7" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3917,7 +3917,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F023387C-ED91-47BD-8E11-5FA5245915F7}" name="PivotTable7" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F023387C-ED91-47BD-8E11-5FA5245915F7}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O20:P31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0">
@@ -4071,559 +4071,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45303852-EBFB-4EB6-9409-416325AD8690}" name="PivotTable10" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C147:D152" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Quantity" fld="9" subtotal="average" baseField="6" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F54FF75E-A4DD-4624-94EA-C9805E6590BC}" name="PivotTable15" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C238:E253" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Quantity" fld="9" subtotal="count" baseField="8" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C94:D111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="17">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F36A9B7-2CC2-4747-B295-29C11DFEDD87}" name="PivotTable14" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C215:E233" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="39">
-        <item x="16"/>
-        <item x="17"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="29"/>
-        <item x="31"/>
-        <item x="30"/>
-        <item x="20"/>
-        <item x="22"/>
-        <item x="21"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="17">
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Sales USD" fld="10" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="1">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="16">
-            <x v="22"/>
-            <x v="23"/>
-            <x v="24"/>
-            <x v="25"/>
-            <x v="26"/>
-            <x v="27"/>
-            <x v="28"/>
-            <x v="29"/>
-            <x v="30"/>
-            <x v="31"/>
-            <x v="32"/>
-            <x v="33"/>
-            <x v="34"/>
-            <x v="35"/>
-            <x v="36"/>
-            <x v="37"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324FA0CB-F108-452F-956F-BD634FC0600F}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324FA0CB-F108-452F-956F-BD634FC0600F}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C24:H64" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4892,8 +4340,488 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45303852-EBFB-4EB6-9409-416325AD8690}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C147:D152" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Quantity" fld="9" subtotal="average" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B167C823-BA6C-4329-B695-C12A7D83A00F}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C115:AP133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="39">
+        <item x="16"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="39">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Sales USD" fld="10" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F54FF75E-A4DD-4624-94EA-C9805E6590BC}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C238:E253" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Quantity" fld="9" subtotal="count" baseField="8" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C17:E20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4974,8 +4902,275 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C11:D13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Product Description" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C94:D111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{035FB879-E106-40E1-9A43-93D438B27AF4}" name="PivotTable11" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C8279AA-1521-48A6-A062-1EF528D5F734}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C137:D142" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Sales Document" fld="3" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{035FB879-E106-40E1-9A43-93D438B27AF4}" name="PivotTable11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C156:D185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5133,8 +5328,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C68:E79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5263,8 +5458,158 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{263FB98E-3725-4EBF-B621-D9B8A3323DDE}" name="PivotTable6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA3A419-CC1C-4656-B774-136C84C8EDBC}" name="PivotTable12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C189:D191" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="39">
+        <item h="1" x="16"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="29"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="20"/>
+        <item h="1" x="22"/>
+        <item h="1" x="21"/>
+        <item h="1" x="35"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="32"/>
+        <item h="1" x="33"/>
+        <item h="1" x="34"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item h="1" x="25"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="5"/>
+        <item x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="9"/>
+        <item h="1" x="8"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="26"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{263FB98E-3725-4EBF-B621-D9B8A3323DDE}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C83:E90" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5422,14 +5767,27 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B167C823-BA6C-4329-B695-C12A7D83A00F}" name="PivotTable8" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C115:AP133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F36A9B7-2CC2-4747-B295-29C11DFEDD87}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C215:E233" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
       <items count="39">
         <item x="16"/>
         <item x="17"/>
@@ -5475,225 +5833,74 @@
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="8"/>
+    <field x="3"/>
   </rowFields>
   <rowItems count="17">
     <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="3"/>
+    <field x="1"/>
   </colFields>
-  <colItems count="39">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <colItems count="2">
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
     </i>
     <i t="grand">
       <x/>
@@ -5702,239 +5909,32 @@
   <dataFields count="1">
     <dataField name="Average of Sales USD" fld="10" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C11:D13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Product Description" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C8279AA-1521-48A6-A062-1EF528D5F734}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C137:D142" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Sales Document" fld="3" subtotal="count" baseField="6" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA3A419-CC1C-4656-B774-136C84C8EDBC}" name="PivotTable12" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C189:D191" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="39">
-        <item h="1" x="16"/>
-        <item h="1" x="17"/>
-        <item h="1" x="19"/>
-        <item h="1" x="18"/>
-        <item h="1" x="29"/>
-        <item h="1" x="31"/>
-        <item h="1" x="30"/>
-        <item h="1" x="20"/>
-        <item h="1" x="22"/>
-        <item h="1" x="21"/>
-        <item h="1" x="35"/>
-        <item h="1" x="36"/>
-        <item h="1" x="37"/>
-        <item h="1" x="26"/>
-        <item h="1" x="27"/>
-        <item h="1" x="28"/>
-        <item h="1" x="32"/>
-        <item h="1" x="33"/>
-        <item h="1" x="34"/>
-        <item h="1" x="23"/>
-        <item h="1" x="24"/>
-        <item h="1" x="25"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="5"/>
-        <item x="6"/>
-        <item h="1" x="7"/>
-        <item h="1" x="9"/>
-        <item h="1" x="8"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="26"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="0" baseItem="0"/>
-  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="16">
+            <x v="22"/>
+            <x v="23"/>
+            <x v="24"/>
+            <x v="25"/>
+            <x v="26"/>
+            <x v="27"/>
+            <x v="28"/>
+            <x v="29"/>
+            <x v="30"/>
+            <x v="31"/>
+            <x v="32"/>
+            <x v="33"/>
+            <x v="34"/>
+            <x v="35"/>
+            <x v="36"/>
+            <x v="37"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5948,7 +5948,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFB86B-ABCE-49FA-AA44-1C6F1E6F10DA}" name="PivotTable13" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFB86B-ABCE-49FA-AA44-1C6F1E6F10DA}" name="PivotTable13" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C196:E210" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>

--- a/Excel/Case Study 2(Pivot Table).xlsx
+++ b/Excel/Case Study 2(Pivot Table).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEAA80E-B1C6-4D12-ADAF-A789CDDAF2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E5817D-06F0-40AB-B134-0DDCBA9FC608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3C2F27DB-59A7-4E77-BCCC-EA28361B83B3}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="66">
   <si>
     <t>Company</t>
   </si>
@@ -239,9 +239,6 @@
   <si>
     <t>Count of Sales Document</t>
   </si>
-  <si>
-    <t>Count of Quantity</t>
-  </si>
 </sst>
 </file>
 
@@ -250,7 +247,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +264,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -419,7 +422,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -477,6 +480,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1 2" xfId="1" xr:uid="{B1476517-8384-4BE4-9D5E-6902BBA44473}"/>
@@ -4071,6 +4082,79 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C11:D13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Product Description" fld="8" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324FA0CB-F108-452F-956F-BD634FC0600F}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C24:H64" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
@@ -4340,7 +4424,60 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45303852-EBFB-4EB6-9409-416325AD8690}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C147:D152" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -4412,7 +4549,235 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C94:D111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA3A419-CC1C-4656-B774-136C84C8EDBC}" name="PivotTable12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C189:D191" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="39">
+        <item h="1" x="16"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="29"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="20"/>
+        <item h="1" x="22"/>
+        <item h="1" x="21"/>
+        <item h="1" x="35"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="32"/>
+        <item h="1" x="33"/>
+        <item h="1" x="34"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item h="1" x="25"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="5"/>
+        <item x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="9"/>
+        <item h="1" x="8"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="26"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B167C823-BA6C-4329-B695-C12A7D83A00F}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C115:AP133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
@@ -4704,911 +5069,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F54FF75E-A4DD-4624-94EA-C9805E6590BC}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C238:E253" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Quantity" fld="9" subtotal="count" baseField="8" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C17:E20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item h="1" x="7"/>
-        <item h="1" x="13"/>
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="9"/>
-        <item h="1" x="11"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="15"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="6"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Quantity" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C11:D13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Product Description" fld="8" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C94:D111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="17">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C8279AA-1521-48A6-A062-1EF528D5F734}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C137:D142" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Sales Document" fld="3" subtotal="count" baseField="6" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{035FB879-E106-40E1-9A43-93D438B27AF4}" name="PivotTable11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C156:D185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="164" showAll="0">
-      <items count="29">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="26"/>
-        <item x="23"/>
-        <item x="27"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="29">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C68:E79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="164" showAll="0">
-      <items count="29">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="26"/>
-        <item x="23"/>
-        <item x="27"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="17">
-        <item h="1" x="7"/>
-        <item h="1" x="13"/>
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="9"/>
-        <item h="1" x="11"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="8"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA3A419-CC1C-4656-B774-136C84C8EDBC}" name="PivotTable12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C189:D191" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="39">
-        <item h="1" x="16"/>
-        <item h="1" x="17"/>
-        <item h="1" x="19"/>
-        <item h="1" x="18"/>
-        <item h="1" x="29"/>
-        <item h="1" x="31"/>
-        <item h="1" x="30"/>
-        <item h="1" x="20"/>
-        <item h="1" x="22"/>
-        <item h="1" x="21"/>
-        <item h="1" x="35"/>
-        <item h="1" x="36"/>
-        <item h="1" x="37"/>
-        <item h="1" x="26"/>
-        <item h="1" x="27"/>
-        <item h="1" x="28"/>
-        <item h="1" x="32"/>
-        <item h="1" x="33"/>
-        <item h="1" x="34"/>
-        <item h="1" x="23"/>
-        <item h="1" x="24"/>
-        <item h="1" x="25"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="5"/>
-        <item x="6"/>
-        <item h="1" x="7"/>
-        <item h="1" x="9"/>
-        <item h="1" x="8"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="26"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{263FB98E-3725-4EBF-B621-D9B8A3323DDE}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C83:E90" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
@@ -5767,7 +5228,345 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C8279AA-1521-48A6-A062-1EF528D5F734}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C137:D142" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Sales Document" fld="3" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{035FB879-E106-40E1-9A43-93D438B27AF4}" name="PivotTable11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C156:D185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="29">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F54FF75E-A4DD-4624-94EA-C9805E6590BC}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C238:E253" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Quantity" fld="9" baseField="8" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F36A9B7-2CC2-4747-B295-29C11DFEDD87}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C215:E233" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
@@ -5935,6 +5734,218 @@
       </pivotArea>
     </format>
   </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C68:E79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="17">
+        <item h="1" x="7"/>
+        <item h="1" x="13"/>
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="11"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C17:E20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item h="1" x="7"/>
+        <item h="1" x="13"/>
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="11"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="6"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Quantity" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -11053,15 +11064,18 @@
     <col min="121" max="121" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B4" s="6">
+    <row r="4" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B4" s="21">
         <v>1</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="22" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C5" s="15" t="s">
         <v>35</v>
       </c>
@@ -11069,7 +11083,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
@@ -11077,7 +11091,7 @@
         <v>9858800</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>37</v>
       </c>
@@ -11085,15 +11099,18 @@
         <v>9858800</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B10" s="6">
+    <row r="10" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B10" s="21">
         <v>2</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C11" s="15" t="s">
         <v>35</v>
       </c>
@@ -11101,7 +11118,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
@@ -11109,7 +11126,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C13" s="9" t="s">
         <v>37</v>
       </c>
@@ -11117,13 +11134,16 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B16" s="6">
+    <row r="16" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B16" s="21">
         <v>3</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="22" t="s">
         <v>19</v>
       </c>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C17" s="15" t="s">
@@ -11167,12 +11187,15 @@
       </c>
     </row>
     <row r="23" spans="2:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B23" s="6">
+      <c r="B23" s="21">
         <v>4</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="22" t="s">
         <v>20</v>
       </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C24" s="15" t="s">
@@ -11647,12 +11670,14 @@
       </c>
     </row>
     <row r="67" spans="2:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="B67" s="6">
+      <c r="B67" s="21">
         <v>5</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="22" t="s">
         <v>22</v>
       </c>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C68" s="15" t="s">
@@ -11783,7 +11808,7 @@
         <v>2123000</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C81" s="15" t="s">
         <v>3</v>
       </c>
@@ -11791,15 +11816,18 @@
         <v>65666</v>
       </c>
     </row>
-    <row r="82" spans="2:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="B82" s="6">
+    <row r="82" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B82" s="21">
         <v>6</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D82" s="23"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="23"/>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C83" s="15" t="s">
         <v>63</v>
       </c>
@@ -11807,7 +11835,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C84" s="15" t="s">
         <v>35</v>
       </c>
@@ -11818,7 +11846,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C85" s="19">
         <v>43984</v>
       </c>
@@ -11829,7 +11857,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C86" s="19">
         <v>43985</v>
       </c>
@@ -11840,7 +11868,7 @@
         <v>235200</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C87" s="19">
         <v>43986</v>
       </c>
@@ -11851,7 +11879,7 @@
         <v>256000</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C88" s="19">
         <v>43987</v>
       </c>
@@ -11862,7 +11890,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C89" s="19">
         <v>43988</v>
       </c>
@@ -11873,7 +11901,7 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C90" s="19" t="s">
         <v>37</v>
       </c>
@@ -11884,15 +11912,17 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="93" spans="2:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="B93" s="6">
+    <row r="93" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B93" s="21">
         <v>7</v>
       </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="22" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D93" s="23"/>
+      <c r="E93" s="23"/>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C94" s="15" t="s">
         <v>35</v>
       </c>
@@ -11900,7 +11930,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C95" s="9" t="s">
         <v>43</v>
       </c>
@@ -11908,7 +11938,7 @@
         <v>1759800</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C96" s="9" t="s">
         <v>53</v>
       </c>
@@ -12037,12 +12067,14 @@
       </c>
     </row>
     <row r="114" spans="2:42" ht="15" x14ac:dyDescent="0.3">
-      <c r="B114" s="6">
+      <c r="B114" s="21">
         <v>8</v>
       </c>
-      <c r="C114" s="17" t="s">
+      <c r="C114" s="22" t="s">
         <v>26</v>
       </c>
+      <c r="D114" s="23"/>
+      <c r="E114" s="23"/>
     </row>
     <row r="115" spans="2:42" x14ac:dyDescent="0.3">
       <c r="C115" s="15" t="s">
@@ -12728,12 +12760,14 @@
       </c>
     </row>
     <row r="136" spans="2:42" ht="15" x14ac:dyDescent="0.3">
-      <c r="B136" s="6">
+      <c r="B136" s="21">
         <v>9</v>
       </c>
-      <c r="C136" s="17" t="s">
+      <c r="C136" s="22" t="s">
         <v>27</v>
       </c>
+      <c r="D136" s="23"/>
+      <c r="E136" s="23"/>
     </row>
     <row r="137" spans="2:42" x14ac:dyDescent="0.3">
       <c r="C137" s="15" t="s">
@@ -12784,10 +12818,10 @@
       </c>
     </row>
     <row r="146" spans="2:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B146" s="6">
+      <c r="B146" s="21">
         <v>10</v>
       </c>
-      <c r="C146" s="17" t="s">
+      <c r="C146" s="22" t="s">
         <v>28</v>
       </c>
     </row>
@@ -12840,10 +12874,10 @@
       </c>
     </row>
     <row r="155" spans="2:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B155" s="6">
+      <c r="B155" s="21">
         <v>11</v>
       </c>
-      <c r="C155" s="17" t="s">
+      <c r="C155" s="22" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13088,10 +13122,10 @@
       </c>
     </row>
     <row r="188" spans="2:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="B188" s="6">
+      <c r="B188" s="21">
         <v>12</v>
       </c>
-      <c r="C188" s="17" t="s">
+      <c r="C188" s="22" t="s">
         <v>31</v>
       </c>
     </row>
@@ -13120,10 +13154,10 @@
       </c>
     </row>
     <row r="195" spans="2:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="B195" s="6">
+      <c r="B195" s="21">
         <v>13</v>
       </c>
-      <c r="C195" s="17" t="s">
+      <c r="C195" s="22" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13290,10 +13324,10 @@
       </c>
     </row>
     <row r="214" spans="2:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="B214" s="6">
+      <c r="B214" s="21">
         <v>14</v>
       </c>
-      <c r="C214" s="17" t="s">
+      <c r="C214" s="22" t="s">
         <v>33</v>
       </c>
     </row>
@@ -13504,16 +13538,16 @@
       </c>
     </row>
     <row r="237" spans="2:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="B237" s="6">
+      <c r="B237" s="21">
         <v>15</v>
       </c>
-      <c r="C237" s="17" t="s">
+      <c r="C237" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C238" s="15" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>59</v>
@@ -13534,154 +13568,154 @@
       <c r="C240" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D240">
-        <v>3</v>
-      </c>
-      <c r="E240">
-        <v>3</v>
+      <c r="D240" s="24">
+        <v>110</v>
+      </c>
+      <c r="E240" s="24">
+        <v>110</v>
       </c>
     </row>
     <row r="241" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C241" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D241">
-        <v>3</v>
-      </c>
-      <c r="E241">
-        <v>3</v>
+      <c r="D241" s="24">
+        <v>150</v>
+      </c>
+      <c r="E241" s="24">
+        <v>150</v>
       </c>
     </row>
     <row r="242" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C242" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D242">
-        <v>1</v>
-      </c>
-      <c r="E242">
-        <v>1</v>
+      <c r="D242" s="24">
+        <v>100</v>
+      </c>
+      <c r="E242" s="24">
+        <v>100</v>
       </c>
     </row>
     <row r="243" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C243" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D243">
-        <v>1</v>
-      </c>
-      <c r="E243">
-        <v>1</v>
+      <c r="D243" s="24">
+        <v>50</v>
+      </c>
+      <c r="E243" s="24">
+        <v>50</v>
       </c>
     </row>
     <row r="244" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C244" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D244">
-        <v>3</v>
-      </c>
-      <c r="E244">
-        <v>3</v>
+      <c r="D244" s="24">
+        <v>210</v>
+      </c>
+      <c r="E244" s="24">
+        <v>210</v>
       </c>
     </row>
     <row r="245" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C245" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D245">
-        <v>2</v>
-      </c>
-      <c r="E245">
-        <v>2</v>
+      <c r="D245" s="24">
+        <v>160</v>
+      </c>
+      <c r="E245" s="24">
+        <v>160</v>
       </c>
     </row>
     <row r="246" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C246" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D246">
-        <v>3</v>
-      </c>
-      <c r="E246">
-        <v>3</v>
+      <c r="D246" s="24">
+        <v>110</v>
+      </c>
+      <c r="E246" s="24">
+        <v>110</v>
       </c>
     </row>
     <row r="247" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C247" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D247">
-        <v>4</v>
-      </c>
-      <c r="E247">
-        <v>4</v>
+      <c r="D247" s="24">
+        <v>310</v>
+      </c>
+      <c r="E247" s="24">
+        <v>310</v>
       </c>
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C248" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D248">
-        <v>1</v>
-      </c>
-      <c r="E248">
-        <v>1</v>
+      <c r="D248" s="24">
+        <v>60</v>
+      </c>
+      <c r="E248" s="24">
+        <v>60</v>
       </c>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C249" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D249">
-        <v>4</v>
-      </c>
-      <c r="E249">
-        <v>4</v>
+      <c r="D249" s="24">
+        <v>640</v>
+      </c>
+      <c r="E249" s="24">
+        <v>640</v>
       </c>
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C250" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D250">
-        <v>10</v>
-      </c>
-      <c r="E250">
-        <v>10</v>
+      <c r="D250" s="24">
+        <v>1430</v>
+      </c>
+      <c r="E250" s="24">
+        <v>1430</v>
       </c>
     </row>
     <row r="251" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C251" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D251">
-        <v>16</v>
-      </c>
-      <c r="E251">
-        <v>16</v>
+      <c r="D251" s="24">
+        <v>2330</v>
+      </c>
+      <c r="E251" s="24">
+        <v>2330</v>
       </c>
     </row>
     <row r="252" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C252" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D252">
-        <v>12</v>
-      </c>
-      <c r="E252">
-        <v>12</v>
+      <c r="D252" s="24">
+        <v>1720</v>
+      </c>
+      <c r="E252" s="24">
+        <v>1720</v>
       </c>
     </row>
     <row r="253" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C253" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D253">
-        <v>63</v>
-      </c>
-      <c r="E253">
-        <v>63</v>
+      <c r="D253" s="24">
+        <v>7380</v>
+      </c>
+      <c r="E253" s="24">
+        <v>7380</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Case Study 2(Pivot Table).xlsx
+++ b/Excel/Case Study 2(Pivot Table).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E5817D-06F0-40AB-B134-0DDCBA9FC608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B46FD8F-9F93-414B-8731-545A4F5C422E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3C2F27DB-59A7-4E77-BCCC-EA28361B83B3}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="66">
   <si>
     <t>Company</t>
   </si>
@@ -881,7 +881,11 @@
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Company" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="1010US"/>
+        <s v="1020US"/>
+        <s v="1040DE"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Company Name" numFmtId="0">
       <sharedItems count="3">
@@ -2455,7 +2459,7 @@
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="105">
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -2469,7 +2473,7 @@
     <n v="172800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -2483,7 +2487,7 @@
     <n v="270000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
@@ -2497,7 +2501,7 @@
     <n v="346800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
@@ -2511,7 +2515,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
@@ -2525,7 +2529,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
@@ -2539,7 +2543,7 @@
     <n v="270000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
@@ -2553,7 +2557,7 @@
     <n v="100000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
@@ -2567,7 +2571,7 @@
     <n v="388800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
@@ -2581,7 +2585,7 @@
     <n v="144000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -2595,7 +2599,7 @@
     <n v="270000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -2609,7 +2613,7 @@
     <n v="361000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -2623,7 +2627,7 @@
     <n v="128000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -2637,7 +2641,7 @@
     <n v="307200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
@@ -2651,7 +2655,7 @@
     <n v="361000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
@@ -2665,7 +2669,7 @@
     <n v="172800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
@@ -2679,7 +2683,7 @@
     <n v="145200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
@@ -2693,7 +2697,7 @@
     <n v="172800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
@@ -2707,7 +2711,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
@@ -2721,7 +2725,7 @@
     <n v="256000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
@@ -2735,7 +2739,7 @@
     <n v="72000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
@@ -2749,7 +2753,7 @@
     <n v="480000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="7"/>
@@ -2763,7 +2767,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="7"/>
@@ -2777,7 +2781,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="8"/>
@@ -2791,7 +2795,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="8"/>
@@ -2805,7 +2809,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="9"/>
@@ -2819,7 +2823,7 @@
     <n v="172800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="9"/>
@@ -2833,7 +2837,7 @@
     <n v="202800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="9"/>
@@ -2847,7 +2851,7 @@
     <n v="144000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="10"/>
@@ -2861,7 +2865,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="10"/>
@@ -2875,7 +2879,7 @@
     <n v="169000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="11"/>
@@ -2889,7 +2893,7 @@
     <n v="172800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="11"/>
@@ -2903,7 +2907,7 @@
     <n v="196000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="11"/>
@@ -2917,7 +2921,7 @@
     <n v="144500"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="12"/>
@@ -2931,7 +2935,7 @@
     <n v="433200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="12"/>
@@ -2945,7 +2949,7 @@
     <n v="196000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="13"/>
@@ -2959,7 +2963,7 @@
     <n v="235200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="13"/>
@@ -2973,7 +2977,7 @@
     <n v="307200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="14"/>
@@ -2987,7 +2991,7 @@
     <n v="433200"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="14"/>
@@ -3001,7 +3005,7 @@
     <n v="202800"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="14"/>
@@ -3015,7 +3019,7 @@
     <n v="196000"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="15"/>
@@ -3029,7 +3033,7 @@
     <n v="180500"/>
   </r>
   <r>
-    <s v="1010US"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="15"/>
@@ -3043,7 +3047,7 @@
     <n v="172800"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
@@ -3057,7 +3061,7 @@
     <n v="202800"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
@@ -3071,7 +3075,7 @@
     <n v="10800"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
@@ -3085,7 +3089,7 @@
     <n v="18000"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
@@ -3099,7 +3103,7 @@
     <n v="179200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="17"/>
@@ -3113,7 +3117,7 @@
     <n v="120000"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="17"/>
@@ -3127,7 +3131,7 @@
     <n v="11200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="17"/>
@@ -3141,7 +3145,7 @@
     <n v="250000"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
@@ -3155,7 +3159,7 @@
     <n v="62500"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
@@ -3169,7 +3173,7 @@
     <n v="19200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
@@ -3183,7 +3187,7 @@
     <n v="58800"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
@@ -3197,7 +3201,7 @@
     <n v="24500"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
@@ -3211,7 +3215,7 @@
     <n v="2800"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
@@ -3225,7 +3229,7 @@
     <n v="115200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
@@ -3239,7 +3243,7 @@
     <n v="88200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
@@ -3253,7 +3257,7 @@
     <n v="88200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
@@ -3267,7 +3271,7 @@
     <n v="115200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
@@ -3281,7 +3285,7 @@
     <n v="88200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
@@ -3295,7 +3299,7 @@
     <n v="21600"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
@@ -3309,7 +3313,7 @@
     <n v="2000"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
@@ -3323,7 +3327,7 @@
     <n v="19200"/>
   </r>
   <r>
-    <s v="1020US"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
@@ -3337,7 +3341,7 @@
     <n v="1200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="20"/>
@@ -3351,7 +3355,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="20"/>
@@ -3365,7 +3369,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="21"/>
@@ -3379,7 +3383,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="21"/>
@@ -3393,7 +3397,7 @@
     <n v="161000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="22"/>
@@ -3407,7 +3411,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="22"/>
@@ -3421,7 +3425,7 @@
     <n v="82000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="22"/>
@@ -3435,7 +3439,7 @@
     <n v="253800"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="23"/>
@@ -3449,7 +3453,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="23"/>
@@ -3463,7 +3467,7 @@
     <n v="176000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="24"/>
@@ -3477,7 +3481,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="24"/>
@@ -3491,7 +3495,7 @@
     <n v="253800"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="24"/>
@@ -3505,7 +3509,7 @@
     <n v="150400"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="25"/>
@@ -3519,7 +3523,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="25"/>
@@ -3533,7 +3537,7 @@
     <n v="253800"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="26"/>
@@ -3547,7 +3551,7 @@
     <n v="82000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="26"/>
@@ -3561,7 +3565,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="27"/>
@@ -3575,7 +3579,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="27"/>
@@ -3589,7 +3593,7 @@
     <n v="161000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="27"/>
@@ -3603,7 +3607,7 @@
     <n v="253800"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="28"/>
@@ -3617,7 +3621,7 @@
     <n v="150400"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="28"/>
@@ -3631,7 +3635,7 @@
     <n v="82000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="29"/>
@@ -3645,7 +3649,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="29"/>
@@ -3659,7 +3663,7 @@
     <n v="161000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="30"/>
@@ -3673,7 +3677,7 @@
     <n v="161000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="30"/>
@@ -3687,7 +3691,7 @@
     <n v="161000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="31"/>
@@ -3701,7 +3705,7 @@
     <n v="161000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="31"/>
@@ -3715,7 +3719,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="31"/>
@@ -3729,7 +3733,7 @@
     <n v="176000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="32"/>
@@ -3743,7 +3747,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="32"/>
@@ -3757,7 +3761,7 @@
     <n v="345100"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="33"/>
@@ -3771,7 +3775,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="33"/>
@@ -3785,7 +3789,7 @@
     <n v="253800"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="33"/>
@@ -3799,7 +3803,7 @@
     <n v="84600"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="34"/>
@@ -3813,7 +3817,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="34"/>
@@ -3827,7 +3831,7 @@
     <n v="176000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="35"/>
@@ -3841,7 +3845,7 @@
     <n v="161000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="35"/>
@@ -3855,7 +3859,7 @@
     <n v="118200"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="36"/>
@@ -3869,7 +3873,7 @@
     <n v="210400"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="36"/>
@@ -3883,7 +3887,7 @@
     <n v="210400"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="36"/>
@@ -3897,7 +3901,7 @@
     <n v="176000"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="37"/>
@@ -3911,7 +3915,7 @@
     <n v="84600"/>
   </r>
   <r>
-    <s v="1040DE"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="1"/>
     <x v="37"/>
@@ -4082,7 +4086,104 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA3A419-CC1C-4656-B774-136C84C8EDBC}" name="PivotTable12" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C189:D191" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="39">
+        <item h="1" x="16"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="29"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="20"/>
+        <item h="1" x="22"/>
+        <item h="1" x="21"/>
+        <item h="1" x="35"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="32"/>
+        <item h="1" x="33"/>
+        <item h="1" x="34"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item h="1" x="25"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="5"/>
+        <item x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="9"/>
+        <item h="1" x="8"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="26"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC674AA5-5854-4859-A6A7-40D76B2128B9}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C11:D13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4154,8 +4255,124 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324FA0CB-F108-452F-956F-BD634FC0600F}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F54FF75E-A4DD-4624-94EA-C9805E6590BC}" name="PivotTable15" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C238:E253" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Quantity" fld="9" baseField="8" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324FA0CB-F108-452F-956F-BD634FC0600F}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C24:H64" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4424,361 +4641,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45303852-EBFB-4EB6-9409-416325AD8690}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C147:D152" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Quantity" fld="9" subtotal="average" baseField="6" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="1">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C94:D111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="17">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCA3A419-CC1C-4656-B774-136C84C8EDBC}" name="PivotTable12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C189:D191" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="39">
-        <item h="1" x="16"/>
-        <item h="1" x="17"/>
-        <item h="1" x="19"/>
-        <item h="1" x="18"/>
-        <item h="1" x="29"/>
-        <item h="1" x="31"/>
-        <item h="1" x="30"/>
-        <item h="1" x="20"/>
-        <item h="1" x="22"/>
-        <item h="1" x="21"/>
-        <item h="1" x="35"/>
-        <item h="1" x="36"/>
-        <item h="1" x="37"/>
-        <item h="1" x="26"/>
-        <item h="1" x="27"/>
-        <item h="1" x="28"/>
-        <item h="1" x="32"/>
-        <item h="1" x="33"/>
-        <item h="1" x="34"/>
-        <item h="1" x="23"/>
-        <item h="1" x="24"/>
-        <item h="1" x="25"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="5"/>
-        <item x="6"/>
-        <item h="1" x="7"/>
-        <item h="1" x="9"/>
-        <item h="1" x="8"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="26"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B167C823-BA6C-4329-B695-C12A7D83A00F}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B167C823-BA6C-4329-B695-C12A7D83A00F}" name="PivotTable8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C115:AP133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5069,505 +4933,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{263FB98E-3725-4EBF-B621-D9B8A3323DDE}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C83:E90" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
-      <items count="39">
-        <item h="1" x="16"/>
-        <item h="1" x="17"/>
-        <item h="1" x="19"/>
-        <item h="1" x="18"/>
-        <item h="1" x="29"/>
-        <item h="1" x="31"/>
-        <item h="1" x="30"/>
-        <item h="1" x="20"/>
-        <item h="1" x="22"/>
-        <item h="1" x="21"/>
-        <item h="1" x="35"/>
-        <item h="1" x="36"/>
-        <item h="1" x="37"/>
-        <item h="1" x="26"/>
-        <item h="1" x="27"/>
-        <item h="1" x="28"/>
-        <item h="1" x="32"/>
-        <item h="1" x="33"/>
-        <item h="1" x="34"/>
-        <item h="1" x="23"/>
-        <item h="1" x="24"/>
-        <item h="1" x="25"/>
-        <item h="1" x="13"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="5"/>
-        <item x="6"/>
-        <item h="1" x="7"/>
-        <item h="1" x="9"/>
-        <item h="1" x="8"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisRow" numFmtId="164" showAll="0">
-      <items count="29">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="26"/>
-        <item x="23"/>
-        <item x="27"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="3" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="4" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C8279AA-1521-48A6-A062-1EF528D5F734}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C137:D142" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Sales Document" fld="3" subtotal="count" baseField="6" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{035FB879-E106-40E1-9A43-93D438B27AF4}" name="PivotTable11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C156:D185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="164" showAll="0">
-      <items count="29">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="26"/>
-        <item x="23"/>
-        <item x="27"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="29">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F54FF75E-A4DD-4624-94EA-C9805E6590BC}" name="PivotTable15" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C238:E253" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Quantity" fld="9" baseField="8" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F36A9B7-2CC2-4747-B295-29C11DFEDD87}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F36A9B7-2CC2-4747-B295-29C11DFEDD87}" name="PivotTable14" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C215:E233" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5709,7 +5076,7 @@
     <dataField name="Average of Sales USD" fld="10" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="16">
@@ -5746,8 +5113,61 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6E9856EB-6D24-4EC7-A8FC-B850103C53C0}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C5:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{839124E5-16C4-48D5-AC53-244D305B7D9B}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C68:E79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5876,8 +5296,297 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{263FB98E-3725-4EBF-B621-D9B8A3323DDE}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C83:D85" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
+      <items count="39">
+        <item h="1" x="16"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="29"/>
+        <item h="1" x="31"/>
+        <item h="1" x="30"/>
+        <item h="1" x="20"/>
+        <item h="1" x="22"/>
+        <item h="1" x="21"/>
+        <item h="1" x="35"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="26"/>
+        <item h="1" x="27"/>
+        <item h="1" x="28"/>
+        <item h="1" x="32"/>
+        <item h="1" x="33"/>
+        <item h="1" x="34"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item h="1" x="25"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="5"/>
+        <item x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="9"/>
+        <item h="1" x="8"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Max of Total Sales" fld="11" subtotal="max" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C8279AA-1521-48A6-A062-1EF528D5F734}" name="PivotTable9" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C137:D142" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Sales Document" fld="3" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45303852-EBFB-4EB6-9409-416325AD8690}" name="PivotTable10" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C147:D152" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Quantity" fld="9" subtotal="average" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D89C0BB-1207-469E-B915-DD1159D54190}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C17:E20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -5958,8 +5667,298 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{035FB879-E106-40E1-9A43-93D438B27AF4}" name="PivotTable11" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C156:D185" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="29">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FB287BA-E5B9-47FF-B943-9EE87482E326}" name="PivotTable7" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C94:D111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFB86B-ABCE-49FA-AA44-1C6F1E6F10DA}" name="PivotTable13" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFB86B-ABCE-49FA-AA44-1C6F1E6F10DA}" name="PivotTable13" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C196:E210" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -11001,8 +11000,8 @@
   <dimension ref="B4:AP253"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
@@ -11810,10 +11809,10 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C81" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="9">
-        <v>65666</v>
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="2:6" ht="15" x14ac:dyDescent="0.3">
@@ -11829,86 +11828,25 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C83" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" t="s">
         <v>63</v>
       </c>
-      <c r="D83" s="15" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C84" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D84" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="C84" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="24">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C85" s="9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C85" s="19">
-        <v>43984</v>
-      </c>
-      <c r="D85">
-        <v>172800</v>
-      </c>
-      <c r="E85">
-        <v>172800</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C86" s="19">
-        <v>43985</v>
-      </c>
-      <c r="D86">
-        <v>235200</v>
-      </c>
-      <c r="E86">
-        <v>235200</v>
-      </c>
-    </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C87" s="19">
-        <v>43986</v>
-      </c>
-      <c r="D87">
-        <v>256000</v>
-      </c>
-      <c r="E87">
-        <v>256000</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C88" s="19">
-        <v>43987</v>
-      </c>
-      <c r="D88">
-        <v>72000</v>
-      </c>
-      <c r="E88">
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C89" s="19">
-        <v>43988</v>
-      </c>
-      <c r="D89">
-        <v>480000</v>
-      </c>
-      <c r="E89">
-        <v>480000</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C90" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D90">
-        <v>480000</v>
-      </c>
-      <c r="E90">
+      <c r="D85" s="24">
         <v>480000</v>
       </c>
     </row>
@@ -13568,10 +13506,10 @@
       <c r="C240" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D240" s="24">
+      <c r="D240">
         <v>110</v>
       </c>
-      <c r="E240" s="24">
+      <c r="E240">
         <v>110</v>
       </c>
     </row>
@@ -13579,10 +13517,10 @@
       <c r="C241" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D241" s="24">
+      <c r="D241">
         <v>150</v>
       </c>
-      <c r="E241" s="24">
+      <c r="E241">
         <v>150</v>
       </c>
     </row>
@@ -13590,10 +13528,10 @@
       <c r="C242" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D242" s="24">
+      <c r="D242">
         <v>100</v>
       </c>
-      <c r="E242" s="24">
+      <c r="E242">
         <v>100</v>
       </c>
     </row>
@@ -13601,10 +13539,10 @@
       <c r="C243" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D243" s="24">
+      <c r="D243">
         <v>50</v>
       </c>
-      <c r="E243" s="24">
+      <c r="E243">
         <v>50</v>
       </c>
     </row>
@@ -13612,10 +13550,10 @@
       <c r="C244" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D244" s="24">
+      <c r="D244">
         <v>210</v>
       </c>
-      <c r="E244" s="24">
+      <c r="E244">
         <v>210</v>
       </c>
     </row>
@@ -13623,10 +13561,10 @@
       <c r="C245" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D245" s="24">
+      <c r="D245">
         <v>160</v>
       </c>
-      <c r="E245" s="24">
+      <c r="E245">
         <v>160</v>
       </c>
     </row>
@@ -13634,10 +13572,10 @@
       <c r="C246" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D246" s="24">
+      <c r="D246">
         <v>110</v>
       </c>
-      <c r="E246" s="24">
+      <c r="E246">
         <v>110</v>
       </c>
     </row>
@@ -13645,10 +13583,10 @@
       <c r="C247" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D247" s="24">
+      <c r="D247">
         <v>310</v>
       </c>
-      <c r="E247" s="24">
+      <c r="E247">
         <v>310</v>
       </c>
     </row>
@@ -13656,10 +13594,10 @@
       <c r="C248" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D248" s="24">
+      <c r="D248">
         <v>60</v>
       </c>
-      <c r="E248" s="24">
+      <c r="E248">
         <v>60</v>
       </c>
     </row>
@@ -13667,10 +13605,10 @@
       <c r="C249" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D249" s="24">
+      <c r="D249">
         <v>640</v>
       </c>
-      <c r="E249" s="24">
+      <c r="E249">
         <v>640</v>
       </c>
     </row>
@@ -13678,10 +13616,10 @@
       <c r="C250" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D250" s="24">
+      <c r="D250">
         <v>1430</v>
       </c>
-      <c r="E250" s="24">
+      <c r="E250">
         <v>1430</v>
       </c>
     </row>
@@ -13689,10 +13627,10 @@
       <c r="C251" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D251" s="24">
+      <c r="D251">
         <v>2330</v>
       </c>
-      <c r="E251" s="24">
+      <c r="E251">
         <v>2330</v>
       </c>
     </row>
@@ -13700,10 +13638,10 @@
       <c r="C252" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D252" s="24">
+      <c r="D252">
         <v>1720</v>
       </c>
-      <c r="E252" s="24">
+      <c r="E252">
         <v>1720</v>
       </c>
     </row>
@@ -13711,10 +13649,10 @@
       <c r="C253" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D253" s="24">
+      <c r="D253">
         <v>7380</v>
       </c>
-      <c r="E253" s="24">
+      <c r="E253">
         <v>7380</v>
       </c>
     </row>
